--- a/database/event/8247/event_8247_evp_summary.xlsx
+++ b/database/event/8247/event_8247_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.5665</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7967</v>
+        <v>2.7297</v>
       </c>
       <c r="E2" t="n">
         <v>7.966</v>
@@ -548,7 +548,7 @@
         <v>1.2337</v>
       </c>
       <c r="D3" t="n">
-        <v>2.113</v>
+        <v>2.0555</v>
       </c>
       <c r="E3" t="n">
         <v>6.2736</v>
@@ -594,7 +594,7 @@
         <v>0.7488</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1169</v>
+        <v>1.0732</v>
       </c>
       <c r="E4" t="n">
         <v>3.8079</v>
@@ -640,7 +640,7 @@
         <v>0.63</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8729</v>
+        <v>0.8324</v>
       </c>
       <c r="E5" t="n">
         <v>3.2037</v>
@@ -686,7 +686,7 @@
         <v>0.5879</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7863</v>
+        <v>0.7471</v>
       </c>
       <c r="E6" t="n">
         <v>2.9895</v>
@@ -732,7 +732,7 @@
         <v>0.4089</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4187</v>
+        <v>0.3845</v>
       </c>
       <c r="E7" t="n">
         <v>2.0794</v>
@@ -778,7 +778,7 @@
         <v>0.3743</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3474</v>
+        <v>0.3143</v>
       </c>
       <c r="E8" t="n">
         <v>1.9031</v>
@@ -824,7 +824,7 @@
         <v>0.2803</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1544</v>
+        <v>0.1239</v>
       </c>
       <c r="E9" t="n">
         <v>1.4252</v>
@@ -870,7 +870,7 @@
         <v>0.2655</v>
       </c>
       <c r="D10" t="n">
-        <v>0.124</v>
+        <v>0.0939</v>
       </c>
       <c r="E10" t="n">
         <v>1.3499</v>
@@ -916,7 +916,7 @@
         <v>0.2642</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1214</v>
+        <v>0.0914</v>
       </c>
       <c r="E11" t="n">
         <v>1.3436</v>
@@ -962,7 +962,7 @@
         <v>0.2455</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0829</v>
+        <v>0.0534</v>
       </c>
       <c r="E12" t="n">
         <v>1.2483</v>
@@ -1008,7 +1008,7 @@
         <v>0.2251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0409</v>
+        <v>0.012</v>
       </c>
       <c r="E13" t="n">
         <v>1.1444</v>
@@ -1054,7 +1054,7 @@
         <v>0.2075</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0049</v>
+        <v>-0.0236</v>
       </c>
       <c r="E14" t="n">
         <v>1.0551</v>
@@ -1100,7 +1100,7 @@
         <v>0.1657</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.081</v>
+        <v>-0.1083</v>
       </c>
       <c r="E15" t="n">
         <v>0.8425</v>
@@ -1146,7 +1146,7 @@
         <v>0.1351</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1439</v>
+        <v>-0.1703</v>
       </c>
       <c r="E16" t="n">
         <v>0.6868</v>
@@ -1192,7 +1192,7 @@
         <v>0.1347</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1446</v>
+        <v>-0.171</v>
       </c>
       <c r="E17" t="n">
         <v>0.6850000000000001</v>
@@ -1238,7 +1238,7 @@
         <v>0.1327</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1488</v>
+        <v>-0.1751</v>
       </c>
       <c r="E18" t="n">
         <v>0.6747</v>
@@ -1284,7 +1284,7 @@
         <v>0.0867</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2433</v>
+        <v>-0.2683</v>
       </c>
       <c r="E19" t="n">
         <v>0.4407</v>
@@ -1330,7 +1330,7 @@
         <v>0.0844</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2479</v>
+        <v>-0.2729</v>
       </c>
       <c r="E20" t="n">
         <v>0.4293</v>
@@ -1376,7 +1376,7 @@
         <v>0.0786</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2599</v>
+        <v>-0.2846</v>
       </c>
       <c r="E21" t="n">
         <v>0.3998</v>
@@ -1422,7 +1422,7 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2637</v>
+        <v>-0.2884</v>
       </c>
       <c r="E22" t="n">
         <v>0.3903</v>
@@ -1468,7 +1468,7 @@
         <v>0.0752</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.267</v>
+        <v>-0.2916</v>
       </c>
       <c r="E23" t="n">
         <v>0.3822</v>
@@ -1514,7 +1514,7 @@
         <v>0.0706</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2763</v>
+        <v>-0.3008</v>
       </c>
       <c r="E24" t="n">
         <v>0.3592</v>
@@ -1560,7 +1560,7 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2915</v>
+        <v>-0.3159</v>
       </c>
       <c r="E25" t="n">
         <v>0.3214</v>
@@ -1606,7 +1606,7 @@
         <v>0.061</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.296</v>
+        <v>-0.3203</v>
       </c>
       <c r="E26" t="n">
         <v>0.3103</v>
@@ -1652,7 +1652,7 @@
         <v>0.057</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3042</v>
+        <v>-0.3284</v>
       </c>
       <c r="E27" t="n">
         <v>0.2899</v>
@@ -1698,7 +1698,7 @@
         <v>0.0474</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3241</v>
+        <v>-0.348</v>
       </c>
       <c r="E28" t="n">
         <v>0.2408</v>
@@ -1744,7 +1744,7 @@
         <v>0.0166</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3872</v>
+        <v>-0.4102</v>
       </c>
       <c r="E29" t="n">
         <v>0.08459999999999999</v>
@@ -1790,7 +1790,7 @@
         <v>0.0113</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3981</v>
+        <v>-0.421</v>
       </c>
       <c r="E30" t="n">
         <v>0.0575</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0198</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4621</v>
+        <v>-0.4841</v>
       </c>
       <c r="E31" t="n">
         <v>-0.1009</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0251</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4729</v>
+        <v>-0.4947</v>
       </c>
       <c r="E32" t="n">
         <v>-0.1275</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0401</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5037</v>
+        <v>-0.5251</v>
       </c>
       <c r="E33" t="n">
         <v>-0.2038</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0563</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5371</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="E34" t="n">
         <v>-0.2864</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0609</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5465</v>
+        <v>-0.5673</v>
       </c>
       <c r="E35" t="n">
         <v>-0.3097</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1054</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.6379</v>
+        <v>-0.6575</v>
       </c>
       <c r="E36" t="n">
         <v>-0.536</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1865</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8045</v>
+        <v>-0.8218</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9485</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2185</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8702</v>
+        <v>-0.8865</v>
       </c>
       <c r="E38" t="n">
         <v>-1.111</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2263</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9025</v>
       </c>
       <c r="E39" t="n">
         <v>-1.151</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2481</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9311</v>
+        <v>-0.9466</v>
       </c>
       <c r="E40" t="n">
         <v>-1.2618</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2557</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E41" t="n">
         <v>-1.3</v>

--- a/database/event/8247/event_8247_evp_summary.xlsx
+++ b/database/event/8247/event_8247_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.966</v>
+        <v>7.6591</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5665</v>
+        <v>1.5062</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7297</v>
+        <v>2.8197</v>
       </c>
       <c r="E2" t="n">
-        <v>7.966</v>
+        <v>7.6591</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.966</v>
+        <v>7.6591</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1277</v>
+        <v>5.489</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1277</v>
+        <v>5.489</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2736</v>
+        <v>5.5627</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2337</v>
+        <v>1.0939</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0555</v>
+        <v>1.8733</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2736</v>
+        <v>5.5627</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2736</v>
+        <v>5.5627</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8259</v>
+        <v>3.9866</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8259</v>
+        <v>3.9866</v>
       </c>
       <c r="N3" t="n">
         <v>225</v>
@@ -584,26 +584,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8079</v>
+        <v>3.6577</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7488</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0732</v>
+        <v>1.0133</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8079</v>
+        <v>3.6577</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8079</v>
+        <v>3.6577</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,44 +612,44 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9291</v>
+        <v>2.6213</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9291</v>
+        <v>2.6213</v>
       </c>
       <c r="N4" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2037</v>
+        <v>3.54</v>
       </c>
       <c r="C5" t="n">
-        <v>0.63</v>
+        <v>0.6962</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8324</v>
+        <v>0.9601</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2037</v>
+        <v>3.54</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2037</v>
+        <v>3.54</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,44 +658,44 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4644</v>
+        <v>2.537</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4644</v>
+        <v>2.537</v>
       </c>
       <c r="N5" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9895</v>
+        <v>3.1989</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5879</v>
+        <v>0.6291</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7471</v>
+        <v>0.8061</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9895</v>
+        <v>3.1989</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9895</v>
+        <v>3.1989</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2996</v>
+        <v>2.2925</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2996</v>
+        <v>2.2925</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -722,26 +722,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.0794</v>
+        <v>2.125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4089</v>
+        <v>0.4179</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3845</v>
+        <v>0.3213</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0794</v>
+        <v>2.125</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0794</v>
+        <v>2.125</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,44 +750,44 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5995</v>
+        <v>1.5229</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5995</v>
+        <v>1.5229</v>
       </c>
       <c r="N7" t="n">
-        <v>152</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9031</v>
+        <v>1.7929</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3743</v>
+        <v>0.3526</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3143</v>
+        <v>0.1714</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9031</v>
+        <v>1.7929</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9031</v>
+        <v>1.7929</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,44 +796,44 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4639</v>
+        <v>1.2849</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4639</v>
+        <v>1.2849</v>
       </c>
       <c r="N8" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4252</v>
+        <v>1.4065</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2803</v>
+        <v>0.2766</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1239</v>
+        <v>-0.003</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4252</v>
+        <v>1.4065</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4252</v>
+        <v>1.4065</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,44 +842,44 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0963</v>
+        <v>1.008</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0963</v>
+        <v>1.008</v>
       </c>
       <c r="N9" t="n">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3499</v>
+        <v>1.3868</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655</v>
+        <v>0.2727</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0939</v>
+        <v>-0.0119</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3499</v>
+        <v>1.3868</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3499</v>
+        <v>1.3868</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0384</v>
+        <v>0.9939</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>134</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0384</v>
+        <v>0.9939</v>
       </c>
       <c r="N10" t="n">
         <v>134</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>JBOEN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3436</v>
+        <v>1.3292</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2642</v>
+        <v>0.2614</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0914</v>
+        <v>-0.0379</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3436</v>
+        <v>1.3292</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3436</v>
+        <v>1.3292</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0335</v>
+        <v>0.9526</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0335</v>
+        <v>0.9526</v>
       </c>
       <c r="N11" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JBOEN</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2483</v>
+        <v>1.1787</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2455</v>
+        <v>0.2318</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0534</v>
+        <v>-0.1059</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2483</v>
+        <v>1.1787</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2483</v>
+        <v>1.1787</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.8447</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.8447</v>
       </c>
       <c r="N12" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1444</v>
+        <v>1.1703</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2251</v>
+        <v>0.2301</v>
       </c>
       <c r="D13" t="n">
-        <v>0.012</v>
+        <v>-0.1097</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1444</v>
+        <v>1.1703</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1444</v>
+        <v>1.1703</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8803</v>
+        <v>0.8387</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8803</v>
+        <v>0.8387</v>
       </c>
       <c r="N13" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0551</v>
+        <v>1.0874</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2075</v>
+        <v>0.2138</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0236</v>
+        <v>-0.1471</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0551</v>
+        <v>1.0874</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0551</v>
+        <v>1.0874</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8116</v>
+        <v>0.7793</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8116</v>
+        <v>0.7793</v>
       </c>
       <c r="N14" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8425</v>
+        <v>0.997</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1657</v>
+        <v>0.1961</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1083</v>
+        <v>-0.1879</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8425</v>
+        <v>0.997</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8425</v>
+        <v>0.997</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,19 +1118,19 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6481</v>
+        <v>0.7145</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6481</v>
+        <v>0.7145</v>
       </c>
       <c r="N15" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6868</v>
+        <v>0.9935</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1351</v>
+        <v>0.1954</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1703</v>
+        <v>-0.1895</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6868</v>
+        <v>0.9935</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6868</v>
+        <v>0.9935</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5283</v>
+        <v>0.712</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>134</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5283</v>
+        <v>0.712</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1182,26 +1182,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jorko</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.9202</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1347</v>
+        <v>0.181</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.171</v>
+        <v>-0.2226</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.9202</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.9202</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5269</v>
+        <v>0.6595</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5269</v>
+        <v>0.6595</v>
       </c>
       <c r="N17" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>Jorko</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6747</v>
+        <v>0.8001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1327</v>
+        <v>0.1573</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1751</v>
+        <v>-0.2768</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6747</v>
+        <v>0.8001</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6747</v>
+        <v>0.8001</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,19 +1256,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.519</v>
+        <v>0.5734</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>0.519</v>
+        <v>0.5734</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4407</v>
+        <v>0.6431</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0867</v>
+        <v>0.1265</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2683</v>
+        <v>-0.3477</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4407</v>
+        <v>0.6431</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4407</v>
+        <v>0.6431</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.339</v>
+        <v>0.4609</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.339</v>
+        <v>0.4609</v>
       </c>
       <c r="N19" t="n">
         <v>79</v>
@@ -1320,26 +1320,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4293</v>
+        <v>0.5393</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0844</v>
+        <v>0.1061</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2729</v>
+        <v>-0.3945</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4293</v>
+        <v>0.5393</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4293</v>
+        <v>0.5393</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3302</v>
+        <v>0.3865</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3302</v>
+        <v>0.3865</v>
       </c>
       <c r="N20" t="n">
-        <v>186</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3998</v>
+        <v>0.521</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0786</v>
+        <v>0.1025</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2846</v>
+        <v>-0.4028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3998</v>
+        <v>0.521</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3998</v>
+        <v>0.521</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3075</v>
+        <v>0.3734</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3075</v>
+        <v>0.3734</v>
       </c>
       <c r="N21" t="n">
-        <v>89</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3903</v>
+        <v>0.4806</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2884</v>
+        <v>-0.421</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3903</v>
+        <v>0.4806</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3903</v>
+        <v>0.4806</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3002</v>
+        <v>0.3444</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>186</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3002</v>
+        <v>0.3444</v>
       </c>
       <c r="N22" t="n">
         <v>186</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3822</v>
+        <v>0.4171</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0752</v>
+        <v>0.082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2916</v>
+        <v>-0.4497</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3822</v>
+        <v>0.4171</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3822</v>
+        <v>0.4171</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.294</v>
+        <v>0.2989</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="M23" t="n">
-        <v>0.294</v>
+        <v>0.2989</v>
       </c>
       <c r="N23" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3592</v>
+        <v>0.3766</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0706</v>
+        <v>0.0741</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3008</v>
+        <v>-0.468</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3592</v>
+        <v>0.3766</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3592</v>
+        <v>0.3766</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2763</v>
+        <v>0.2699</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2763</v>
+        <v>0.2699</v>
       </c>
       <c r="N24" t="n">
-        <v>38</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3214</v>
+        <v>0.3635</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3159</v>
+        <v>-0.4739</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3214</v>
+        <v>0.3635</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3214</v>
+        <v>0.3635</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,19 +1578,19 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2472</v>
+        <v>0.2605</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2472</v>
+        <v>0.2605</v>
       </c>
       <c r="N25" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3103</v>
+        <v>0.3629</v>
       </c>
       <c r="C26" t="n">
-        <v>0.061</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3203</v>
+        <v>-0.4742</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3103</v>
+        <v>0.3629</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3103</v>
+        <v>0.3629</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2387</v>
+        <v>0.2601</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>69</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2387</v>
+        <v>0.2601</v>
       </c>
       <c r="N26" t="n">
         <v>69</v>
@@ -1642,26 +1642,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2899</v>
+        <v>0.3356</v>
       </c>
       <c r="C27" t="n">
-        <v>0.057</v>
+        <v>0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3284</v>
+        <v>-0.4865</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2899</v>
+        <v>0.3356</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2899</v>
+        <v>0.3356</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.223</v>
+        <v>0.2405</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>0.223</v>
+        <v>0.2405</v>
       </c>
       <c r="N27" t="n">
-        <v>79</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2408</v>
+        <v>0.3275</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0474</v>
+        <v>0.0644</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.348</v>
+        <v>-0.4902</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2408</v>
+        <v>0.3275</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2408</v>
+        <v>0.3275</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1852</v>
+        <v>0.2347</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1852</v>
+        <v>0.2347</v>
       </c>
       <c r="N28" t="n">
-        <v>134</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DarkMeister</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.3144</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0166</v>
+        <v>0.0618</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4102</v>
+        <v>-0.4961</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.3144</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.3144</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2253</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2253</v>
       </c>
       <c r="N29" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0575</v>
+        <v>0.284</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0113</v>
+        <v>0.0558</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.421</v>
+        <v>-0.5098</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0575</v>
+        <v>0.284</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0575</v>
+        <v>0.284</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0442</v>
+        <v>0.2035</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0442</v>
+        <v>0.2035</v>
       </c>
       <c r="N30" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>DarkMeister</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1009</v>
+        <v>0.26</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0198</v>
+        <v>0.0511</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4841</v>
+        <v>-0.5206</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1009</v>
+        <v>0.26</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1009</v>
+        <v>0.26</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,44 +1854,44 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0776</v>
+        <v>0.1863</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0776</v>
+        <v>0.1863</v>
       </c>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1275</v>
+        <v>0.2196</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0251</v>
+        <v>0.0432</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4947</v>
+        <v>-0.5389</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1275</v>
+        <v>0.2196</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1275</v>
+        <v>0.2196</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.1574</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.1574</v>
       </c>
       <c r="N32" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2038</v>
+        <v>0.0579</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0401</v>
+        <v>0.0114</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5251</v>
+        <v>-0.6119</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2038</v>
+        <v>0.0579</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2038</v>
+        <v>0.0579</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1568</v>
+        <v>0.0415</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1568</v>
+        <v>0.0415</v>
       </c>
       <c r="N33" t="n">
-        <v>225</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2864</v>
+        <v>-0.0105</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0563</v>
+        <v>-0.0021</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.6428</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2864</v>
+        <v>-0.0105</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2864</v>
+        <v>-0.0105</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,19 +1992,19 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2203</v>
+        <v>-0.0075</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2203</v>
+        <v>-0.0075</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3097</v>
+        <v>-0.0324</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0609</v>
+        <v>-0.0064</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5673</v>
+        <v>-0.6526</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3097</v>
+        <v>-0.0324</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3097</v>
+        <v>-0.0324</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2382</v>
+        <v>-0.0232</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2382</v>
+        <v>-0.0232</v>
       </c>
       <c r="N35" t="n">
         <v>38</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.536</v>
+        <v>-0.2876</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1054</v>
+        <v>-0.0566</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.6575</v>
+        <v>-0.7679</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.536</v>
+        <v>-0.2876</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.536</v>
+        <v>-0.2876</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4123</v>
+        <v>-0.2061</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>79</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4123</v>
+        <v>-0.2061</v>
       </c>
       <c r="N36" t="n">
         <v>79</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9485</v>
+        <v>-0.2891</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1865</v>
+        <v>-0.0569</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8218</v>
+        <v>-0.7685</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9485</v>
+        <v>-0.2891</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9485</v>
+        <v>-0.2891</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7296</v>
+        <v>-0.2072</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>152</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7296</v>
+        <v>-0.2072</v>
       </c>
       <c r="N37" t="n">
         <v>152</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.111</v>
+        <v>-0.7186</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2185</v>
+        <v>-0.1413</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8865</v>
+        <v>-0.9624</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.111</v>
+        <v>-0.7186</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.111</v>
+        <v>-0.7186</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8546</v>
+        <v>-0.515</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>89</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8546</v>
+        <v>-0.515</v>
       </c>
       <c r="N38" t="n">
         <v>89</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.151</v>
+        <v>-0.7518</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2263</v>
+        <v>-0.1478</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9025</v>
+        <v>-0.9774</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.151</v>
+        <v>-0.7518</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.151</v>
+        <v>-0.7518</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8854</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>69</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8854</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2618</v>
+        <v>-0.8855</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2481</v>
+        <v>-0.1741</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9466</v>
+        <v>-1.0378</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2618</v>
+        <v>-0.8855</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.2618</v>
+        <v>-0.8855</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9706</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9706</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>38</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3</v>
+        <v>-1.296</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2557</v>
+        <v>-0.2549</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.9618</v>
+        <v>-1.2231</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3</v>
+        <v>-1.296</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.3</v>
+        <v>-1.296</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.9288</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>-1</v>
+        <v>-0.9288</v>
       </c>
       <c r="N41" t="n">
         <v>38</v>
@@ -2429,10 +2429,10 @@
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2678</v>
+        <v>0.275</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6238</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1278</v>
+        <v>-0.1082</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.6838</v>
+        <v>-2.2722</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2676</v>
+        <v>-0.1814</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.6196</v>
+        <v>-3.8094</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3997</v>
+        <v>-0.2601</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.393700000000001</v>
+        <v>-5.4621</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5413</v>
+        <v>-0.3557</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.3673</v>
+        <v>-7.4697</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9295</v>
+        <v>1.6242</v>
       </c>
       <c r="J7" t="n">
-        <v>40.5195</v>
+        <v>34.1082</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0242</v>
+        <v>1.0215</v>
       </c>
       <c r="J8" t="n">
-        <v>21.5082</v>
+        <v>21.4515</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3167</v>
+        <v>0.3964</v>
       </c>
       <c r="J9" t="n">
-        <v>6.6507</v>
+        <v>8.324400000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0876</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8396</v>
+        <v>-0.2079</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6244</v>
+        <v>-0.5587</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.1124</v>
+        <v>-11.7327</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0857</v>
+        <v>-0.0963</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4569</v>
+        <v>-1.6371</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0857</v>
+        <v>-0.0963</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4569</v>
+        <v>-1.6371</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6</v>
+        <v>-0.4059</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.2</v>
+        <v>-6.9003</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6418</v>
+        <v>-0.434</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.9106</v>
+        <v>-7.378</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.4527</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.3713</v>
+        <v>-7.6959</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7939</v>
+        <v>1.5262</v>
       </c>
       <c r="J17" t="n">
-        <v>30.4963</v>
+        <v>25.9454</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6539</v>
+        <v>1.4339</v>
       </c>
       <c r="J18" t="n">
-        <v>28.1163</v>
+        <v>24.3763</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6922</v>
+        <v>0.7992</v>
       </c>
       <c r="J19" t="n">
-        <v>11.7674</v>
+        <v>13.5864</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2661</v>
+        <v>0.3647</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5237</v>
+        <v>6.1999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4136</v>
+        <v>-0.3299</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.0312</v>
+        <v>-5.6083</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5677</v>
+        <v>0.4922</v>
       </c>
       <c r="J22" t="n">
-        <v>12.4894</v>
+        <v>10.8284</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4779</v>
+        <v>0.4102</v>
       </c>
       <c r="J23" t="n">
-        <v>10.5138</v>
+        <v>9.0244</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0673</v>
+        <v>0.0853</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4806</v>
+        <v>1.8766</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0202</v>
+        <v>0.0121</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4444</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.92</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2276</v>
+        <v>-0.1255</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.0072</v>
+        <v>-2.761</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3519</v>
+        <v>0.2982</v>
       </c>
       <c r="J27" t="n">
-        <v>7.7418</v>
+        <v>6.5604</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1469</v>
+        <v>0.1028</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2318</v>
+        <v>2.2616</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.9094</v>
+        <v>-2.5366</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3784</v>
+        <v>-0.2398</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.3248</v>
+        <v>-5.2756</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4778</v>
+        <v>-0.3081</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.5116</v>
+        <v>-6.7782</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5702</v>
+        <v>0.6845</v>
       </c>
       <c r="J32" t="n">
-        <v>13.1146</v>
+        <v>15.7435</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1104</v>
+        <v>-0.0046</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1941</v>
+        <v>-0.1121</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.4643</v>
+        <v>-2.5783</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2291</v>
+        <v>-0.1347</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.2693</v>
+        <v>-3.0981</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2945</v>
+        <v>-0.1779</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.7735</v>
+        <v>-4.0917</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0763</v>
+        <v>1.0417</v>
       </c>
       <c r="J37" t="n">
-        <v>24.7549</v>
+        <v>23.9591</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8578</v>
+        <v>0.8415</v>
       </c>
       <c r="J38" t="n">
-        <v>19.7294</v>
+        <v>19.3545</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.98</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1936</v>
+        <v>-0.1251</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.4528</v>
+        <v>-2.8773</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.98</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1936</v>
+        <v>-0.1251</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.4528</v>
+        <v>-2.8773</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3328</v>
+        <v>-0.2629</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.6544</v>
+        <v>-6.0467</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.4767</v>
       </c>
       <c r="J42" t="n">
-        <v>12.3633</v>
+        <v>9.0573</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5783</v>
+        <v>0.4376</v>
       </c>
       <c r="J43" t="n">
-        <v>10.9877</v>
+        <v>8.314399999999999</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3924</v>
+        <v>0.3428</v>
       </c>
       <c r="J44" t="n">
-        <v>7.4556</v>
+        <v>6.5132</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2268</v>
+        <v>0.2308</v>
       </c>
       <c r="J45" t="n">
-        <v>4.3092</v>
+        <v>4.3852</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4083</v>
+        <v>-0.2515</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.7577</v>
+        <v>-4.7785</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3948</v>
+        <v>0.3362</v>
       </c>
       <c r="J47" t="n">
-        <v>7.5012</v>
+        <v>6.3878</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.076</v>
+        <v>0.04</v>
       </c>
       <c r="J48" t="n">
-        <v>1.444</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1332</v>
+        <v>-0.0936</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.5308</v>
+        <v>-1.7784</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.77</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4087</v>
+        <v>-0.2601</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.7653</v>
+        <v>-4.9419</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4512</v>
+        <v>-0.2893</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.572800000000001</v>
+        <v>-5.4967</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4731</v>
+        <v>0.4617</v>
       </c>
       <c r="J52" t="n">
-        <v>10.4082</v>
+        <v>10.1574</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3744</v>
+        <v>0.3851</v>
       </c>
       <c r="J53" t="n">
-        <v>8.236800000000001</v>
+        <v>8.472200000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1886</v>
+        <v>-0.1171</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.1492</v>
+        <v>-2.5762</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4688</v>
+        <v>-0.301</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.3136</v>
+        <v>-6.622</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5744</v>
+        <v>-0.3768</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.6368</v>
+        <v>-8.2896</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.3</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8316</v>
+        <v>0.6178</v>
       </c>
       <c r="J57" t="n">
-        <v>18.2952</v>
+        <v>13.5916</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7134</v>
+        <v>0.5476</v>
       </c>
       <c r="J58" t="n">
-        <v>15.6948</v>
+        <v>12.0472</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3424</v>
+        <v>0.3565</v>
       </c>
       <c r="J59" t="n">
-        <v>7.5328</v>
+        <v>7.843</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1366</v>
       </c>
       <c r="J60" t="n">
-        <v>1.8172</v>
+        <v>3.0052</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3351</v>
+        <v>-0.2645</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.3722</v>
+        <v>-5.819</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I62" t="n">
-        <v>0.418</v>
+        <v>0.4162</v>
       </c>
       <c r="J62" t="n">
-        <v>9.196</v>
+        <v>9.1564</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1702</v>
+        <v>0.1535</v>
       </c>
       <c r="J63" t="n">
-        <v>3.7444</v>
+        <v>3.377</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.78</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3744</v>
+        <v>-0.2423</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.236800000000001</v>
+        <v>-5.3306</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5448</v>
+        <v>-0.3576</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.9856</v>
+        <v>-7.8672</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5448</v>
+        <v>-0.3576</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.9856</v>
+        <v>-7.8672</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5427</v>
+        <v>1.0781</v>
       </c>
       <c r="J67" t="n">
-        <v>33.9394</v>
+        <v>23.7182</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.33</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8546</v>
+        <v>0.6431</v>
       </c>
       <c r="J68" t="n">
-        <v>18.8012</v>
+        <v>14.1482</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8084</v>
+        <v>0.6163</v>
       </c>
       <c r="J69" t="n">
-        <v>17.7848</v>
+        <v>13.5586</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2014</v>
+        <v>0.2711</v>
       </c>
       <c r="J70" t="n">
-        <v>4.4308</v>
+        <v>5.9642</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0427</v>
+        <v>-1.023</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.9394</v>
+        <v>-22.506</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2234</v>
+        <v>0.2166</v>
       </c>
       <c r="J72" t="n">
-        <v>4.2446</v>
+        <v>4.1154</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1848</v>
+        <v>0.1679</v>
       </c>
       <c r="J73" t="n">
-        <v>3.5112</v>
+        <v>3.1901</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0822</v>
+        <v>0.0443</v>
       </c>
       <c r="J74" t="n">
-        <v>1.5618</v>
+        <v>0.8417</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.54</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4645</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.129</v>
+        <v>-8.8255</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7279</v>
+        <v>-0.4921</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.8301</v>
+        <v>-9.3499</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3179</v>
+        <v>0.9354</v>
       </c>
       <c r="J77" t="n">
-        <v>25.0401</v>
+        <v>17.7726</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.53</v>
       </c>
       <c r="I78" t="n">
-        <v>1.2394</v>
+        <v>0.8859</v>
       </c>
       <c r="J78" t="n">
-        <v>23.5486</v>
+        <v>16.8321</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5125</v>
+        <v>0.4863</v>
       </c>
       <c r="J79" t="n">
-        <v>9.737500000000001</v>
+        <v>9.239699999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1708</v>
+        <v>0.2532</v>
       </c>
       <c r="J80" t="n">
-        <v>3.2452</v>
+        <v>4.8108</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0161</v>
+        <v>0.0631</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.3059</v>
+        <v>1.1989</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5202</v>
+        <v>0.401</v>
       </c>
       <c r="J82" t="n">
-        <v>11.4444</v>
+        <v>8.821999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3994</v>
+        <v>0.3351</v>
       </c>
       <c r="J83" t="n">
-        <v>8.786799999999999</v>
+        <v>7.3722</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3262</v>
+        <v>0.2777</v>
       </c>
       <c r="J84" t="n">
-        <v>7.1764</v>
+        <v>6.1094</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0706</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>1.5532</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.421</v>
+        <v>-0.262</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.262</v>
+        <v>-5.764</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2345</v>
+        <v>0.186</v>
       </c>
       <c r="J87" t="n">
-        <v>5.159</v>
+        <v>4.092</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1806</v>
+        <v>0.1357</v>
       </c>
       <c r="J88" t="n">
-        <v>3.9732</v>
+        <v>2.9854</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1806</v>
+        <v>0.1357</v>
       </c>
       <c r="J89" t="n">
-        <v>3.9732</v>
+        <v>2.9854</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3526</v>
+        <v>-0.2216</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.7572</v>
+        <v>-4.8752</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5475</v>
+        <v>-0.3573</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.045</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4172</v>
+        <v>0.4229</v>
       </c>
       <c r="J92" t="n">
-        <v>10.0128</v>
+        <v>10.1496</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2839</v>
+        <v>0.3178</v>
       </c>
       <c r="J93" t="n">
-        <v>6.8136</v>
+        <v>7.6272</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.04</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1008</v>
+        <v>0.1118</v>
       </c>
       <c r="J94" t="n">
-        <v>2.4192</v>
+        <v>2.6832</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2686</v>
+        <v>-0.1591</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4464</v>
+        <v>-3.8184</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3309</v>
+        <v>-0.2013</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.9416</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2424</v>
+        <v>0.8736</v>
       </c>
       <c r="J97" t="n">
-        <v>29.8176</v>
+        <v>20.9664</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6614</v>
+        <v>0.5006</v>
       </c>
       <c r="J98" t="n">
-        <v>15.8736</v>
+        <v>12.0144</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4878</v>
+        <v>-0.4366</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.7072</v>
+        <v>-10.4784</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7208</v>
+        <v>-0.6758</v>
       </c>
       <c r="J100" t="n">
-        <v>-17.2992</v>
+        <v>-16.2192</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8164</v>
+        <v>-0.7773</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.5936</v>
+        <v>-18.6552</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8162</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>18.7726</v>
+        <v>13.064</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4122</v>
+        <v>0.3399</v>
       </c>
       <c r="J103" t="n">
-        <v>9.480600000000001</v>
+        <v>7.8177</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0643</v>
+        <v>0.0745</v>
       </c>
       <c r="J104" t="n">
-        <v>1.4789</v>
+        <v>1.7135</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.8895</v>
+        <v>-5.4763</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4687</v>
+        <v>-0.2973</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.7801</v>
+        <v>-6.8379</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6241</v>
+        <v>0.4788</v>
       </c>
       <c r="J107" t="n">
-        <v>14.3543</v>
+        <v>11.0124</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.008</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>0.184</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.036</v>
+        <v>-1.7273</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3524</v>
+        <v>-0.2179</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.1052</v>
+        <v>-5.0117</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3672</v>
+        <v>-0.228</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.445600000000001</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7033</v>
+        <v>0.6494</v>
       </c>
       <c r="J112" t="n">
-        <v>25.3188</v>
+        <v>23.3784</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1509</v>
+        <v>0.1911</v>
       </c>
       <c r="J113" t="n">
-        <v>5.4324</v>
+        <v>6.8796</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0395</v>
+        <v>-0.0068</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.422</v>
+        <v>-0.2448</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0395</v>
+        <v>-0.0068</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.422</v>
+        <v>-0.2448</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.85</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3279</v>
+        <v>-0.1969</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.8044</v>
+        <v>-7.0884</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.61</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4682</v>
+        <v>1.0266</v>
       </c>
       <c r="J117" t="n">
-        <v>52.8552</v>
+        <v>36.9576</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.15</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4423</v>
+        <v>0.401</v>
       </c>
       <c r="J118" t="n">
-        <v>15.9228</v>
+        <v>14.436</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3695</v>
+        <v>0.3713</v>
       </c>
       <c r="J119" t="n">
-        <v>13.302</v>
+        <v>13.3668</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3683</v>
+        <v>-0.2974</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.2588</v>
+        <v>-10.7064</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.86</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5635</v>
+        <v>-0.4996</v>
       </c>
       <c r="J121" t="n">
-        <v>-20.286</v>
+        <v>-17.9856</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.12</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2568</v>
+        <v>0.2835</v>
       </c>
       <c r="J122" t="n">
-        <v>7.704</v>
+        <v>8.505000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2402</v>
+        <v>0.2636</v>
       </c>
       <c r="J123" t="n">
-        <v>7.206</v>
+        <v>7.908</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2232</v>
+        <v>0.2435</v>
       </c>
       <c r="J124" t="n">
-        <v>6.696</v>
+        <v>7.305</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1195</v>
+        <v>-0.0644</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.585</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4286</v>
+        <v>-0.2701</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.858</v>
+        <v>-8.103</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.5857</v>
       </c>
       <c r="J127" t="n">
-        <v>23.634</v>
+        <v>17.571</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4832</v>
+        <v>0.4081</v>
       </c>
       <c r="J128" t="n">
-        <v>14.496</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1466</v>
+        <v>0.1802</v>
       </c>
       <c r="J129" t="n">
-        <v>4.398</v>
+        <v>5.406</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="J130" t="n">
-        <v>2.187</v>
+        <v>3.399</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3776</v>
+        <v>-0.3137</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.328</v>
+        <v>-9.411</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0943</v>
+        <v>0.7842</v>
       </c>
       <c r="J132" t="n">
-        <v>30.6404</v>
+        <v>21.9576</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7857</v>
+        <v>0.5962</v>
       </c>
       <c r="J133" t="n">
-        <v>21.9996</v>
+        <v>16.6936</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.2</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5589</v>
+        <v>0.4701</v>
       </c>
       <c r="J134" t="n">
-        <v>15.6492</v>
+        <v>13.1628</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0274</v>
+        <v>0.092</v>
       </c>
       <c r="J135" t="n">
-        <v>0.7672</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.467</v>
+        <v>-0.3959</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.076</v>
+        <v>-11.0852</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1701</v>
+        <v>0.1608</v>
       </c>
       <c r="J137" t="n">
-        <v>4.7628</v>
+        <v>4.5024</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1501</v>
+        <v>0.1368</v>
       </c>
       <c r="J138" t="n">
-        <v>4.2028</v>
+        <v>3.8304</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="J139" t="n">
-        <v>2.2708</v>
+        <v>1.554</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3908</v>
+        <v>-0.2487</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.9424</v>
+        <v>-6.9636</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5031</v>
+        <v>-0.3262</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.0868</v>
+        <v>-9.133599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.28</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5308</v>
+        <v>0.4202</v>
       </c>
       <c r="J142" t="n">
-        <v>10.616</v>
+        <v>8.404</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.307</v>
+        <v>-0.1963</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.14</v>
+        <v>-3.926</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3231</v>
+        <v>-0.2064</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.462</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3696</v>
+        <v>-0.2363</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.392</v>
+        <v>-4.726</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4141</v>
+        <v>-0.2658</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.282</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.68</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="J147" t="n">
-        <v>17.61</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.46</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6347</v>
+        <v>0.471</v>
       </c>
       <c r="J148" t="n">
-        <v>12.694</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.4</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5615</v>
+        <v>0.4326</v>
       </c>
       <c r="J149" t="n">
-        <v>11.23</v>
+        <v>8.651999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2016</v>
+        <v>-0.1033</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.032</v>
+        <v>-2.066</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3159</v>
+        <v>-0.184</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.318</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4561</v>
+        <v>1.0201</v>
       </c>
       <c r="J152" t="n">
-        <v>30.5781</v>
+        <v>21.4221</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.14</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3511</v>
+        <v>0.3797</v>
       </c>
       <c r="J153" t="n">
-        <v>7.3731</v>
+        <v>7.9737</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2372</v>
+        <v>0.3029</v>
       </c>
       <c r="J154" t="n">
-        <v>4.9812</v>
+        <v>6.3609</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.08</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1781</v>
+        <v>0.2453</v>
       </c>
       <c r="J155" t="n">
-        <v>3.7401</v>
+        <v>5.1513</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0843</v>
+        <v>0.1528</v>
       </c>
       <c r="J156" t="n">
-        <v>1.7703</v>
+        <v>3.2088</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2309</v>
+        <v>0.2335</v>
       </c>
       <c r="J157" t="n">
-        <v>4.8489</v>
+        <v>4.9035</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1347</v>
+        <v>0.1158</v>
       </c>
       <c r="J158" t="n">
-        <v>2.8287</v>
+        <v>2.4318</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1565</v>
+        <v>-0.1139</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.2865</v>
+        <v>-2.3919</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.293</v>
+        <v>-0.1868</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.153</v>
+        <v>-3.9228</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5661</v>
+        <v>-0.3717</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.8881</v>
+        <v>-7.8057</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.39</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6022</v>
+        <v>0.445</v>
       </c>
       <c r="J162" t="n">
-        <v>13.8506</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2385</v>
+        <v>0.2029</v>
       </c>
       <c r="J163" t="n">
-        <v>5.4855</v>
+        <v>4.6667</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.04</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0581</v>
+        <v>0.0726</v>
       </c>
       <c r="J164" t="n">
-        <v>1.3363</v>
+        <v>1.6698</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.99</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0796</v>
+        <v>-0.0297</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.8308</v>
+        <v>-0.6831</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.185</v>
+        <v>-0.0985</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.255</v>
+        <v>-2.2655</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4485</v>
+        <v>0.3706</v>
       </c>
       <c r="J167" t="n">
-        <v>10.3155</v>
+        <v>8.5238</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4063</v>
+        <v>0.3447</v>
       </c>
       <c r="J168" t="n">
-        <v>9.344900000000001</v>
+        <v>7.9281</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.0991</v>
+        <v>-3.1786</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.0991</v>
+        <v>-3.1786</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.47</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.5401</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.1884</v>
+        <v>-12.4223</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.37</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5857</v>
+        <v>0.5553</v>
       </c>
       <c r="J172" t="n">
-        <v>23.428</v>
+        <v>22.212</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.33</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5354</v>
+        <v>0.5161</v>
       </c>
       <c r="J173" t="n">
-        <v>21.416</v>
+        <v>20.644</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1062</v>
       </c>
       <c r="J174" t="n">
-        <v>2.74</v>
+        <v>4.248</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.84</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3411</v>
+        <v>-0.2064</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.644</v>
+        <v>-8.256</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.78</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4265</v>
+        <v>-0.2669</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.06</v>
+        <v>-10.676</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.42</v>
+        <v>0.9947</v>
       </c>
       <c r="J177" t="n">
-        <v>56.8</v>
+        <v>39.788</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5139</v>
+        <v>0.443</v>
       </c>
       <c r="J178" t="n">
-        <v>20.556</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3205</v>
+        <v>0.3536</v>
       </c>
       <c r="J179" t="n">
-        <v>12.82</v>
+        <v>14.144</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2604</v>
+        <v>0.3121</v>
       </c>
       <c r="J180" t="n">
-        <v>10.416</v>
+        <v>12.484</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.6901</v>
       </c>
       <c r="J181" t="n">
-        <v>-29.696</v>
+        <v>-27.604</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7074</v>
+        <v>0.6552</v>
       </c>
       <c r="J182" t="n">
-        <v>11.3184</v>
+        <v>10.4832</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3097</v>
+        <v>-0.2026</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.9552</v>
+        <v>-3.2416</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4477</v>
+        <v>-0.2907</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.1632</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4619</v>
+        <v>-0.3003</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.3904</v>
+        <v>-4.8048</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5707</v>
+        <v>-0.3761</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.1312</v>
+        <v>-6.0176</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.9745</v>
+        <v>1.5161</v>
       </c>
       <c r="J187" t="n">
-        <v>31.592</v>
+        <v>24.2576</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.32</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6969</v>
+        <v>0.6092</v>
       </c>
       <c r="J188" t="n">
-        <v>11.1504</v>
+        <v>9.747199999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5961</v>
       </c>
       <c r="J189" t="n">
-        <v>10.7824</v>
+        <v>9.537599999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4172</v>
+        <v>0.4439</v>
       </c>
       <c r="J190" t="n">
-        <v>6.6752</v>
+        <v>7.1024</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0795</v>
+        <v>0.1691</v>
       </c>
       <c r="J191" t="n">
-        <v>1.272</v>
+        <v>2.7056</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9207</v>
+        <v>0.8363</v>
       </c>
       <c r="J192" t="n">
-        <v>18.414</v>
+        <v>16.726</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.06</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1814</v>
+        <v>0.1779</v>
       </c>
       <c r="J193" t="n">
-        <v>3.628</v>
+        <v>3.558</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3368</v>
+        <v>-0.2112</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.736</v>
+        <v>-4.224</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6234</v>
+        <v>-0.413</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.468</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6726</v>
+        <v>-0.4498</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.452</v>
+        <v>-8.996</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.7942</v>
+        <v>1.2895</v>
       </c>
       <c r="J197" t="n">
-        <v>35.884</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="J198" t="n">
-        <v>18.68</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4702</v>
+        <v>0.4598</v>
       </c>
       <c r="J199" t="n">
-        <v>9.404</v>
+        <v>9.196</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.01</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.0895</v>
+        <v>-0.0113</v>
       </c>
       <c r="J200" t="n">
-        <v>-1.79</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4684</v>
+        <v>-0.3916</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.368</v>
+        <v>-7.832</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3852</v>
+        <v>0.3898</v>
       </c>
       <c r="J202" t="n">
-        <v>6.9336</v>
+        <v>7.0164</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0949</v>
+        <v>0.0568</v>
       </c>
       <c r="J203" t="n">
-        <v>1.7082</v>
+        <v>1.0224</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3938</v>
+        <v>-0.2629</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.0884</v>
+        <v>-4.7322</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.58</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6338</v>
+        <v>-0.4234</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.4084</v>
+        <v>-7.6212</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7099</v>
+        <v>-0.479</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.7782</v>
+        <v>-8.622</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.2</v>
       </c>
       <c r="I207" t="n">
-        <v>2.0897</v>
+        <v>1.6661</v>
       </c>
       <c r="J207" t="n">
-        <v>37.6146</v>
+        <v>29.9898</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.41</v>
       </c>
       <c r="I208" t="n">
-        <v>0.974</v>
+        <v>0.7302</v>
       </c>
       <c r="J208" t="n">
-        <v>17.532</v>
+        <v>13.1436</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.09</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1599</v>
+        <v>0.2458</v>
       </c>
       <c r="J209" t="n">
-        <v>2.8782</v>
+        <v>4.4244</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2191</v>
+        <v>-0.1323</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.9438</v>
+        <v>-2.3814</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4802</v>
+        <v>-0.4024</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.643599999999999</v>
+        <v>-7.2432</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8247/event_8247_evp_summary.xlsx
+++ b/database/event/8247/event_8247_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6591</v>
+        <v>7.637</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5062</v>
+        <v>1.5018</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8197</v>
+        <v>2.8523</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6591</v>
+        <v>7.637</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6591</v>
+        <v>7.637</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5.489</v>
+        <v>6.0032</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>5.489</v>
+        <v>6.0032</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5627</v>
+        <v>5.5078</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0939</v>
+        <v>1.0831</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8733</v>
+        <v>1.8831</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5627</v>
+        <v>5.5078</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5627</v>
+        <v>5.5078</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9866</v>
+        <v>4.3295</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9866</v>
+        <v>4.3295</v>
       </c>
       <c r="N3" t="n">
         <v>225</v>
@@ -584,26 +584,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6577</v>
+        <v>3.5807</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7042</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0133</v>
+        <v>1.0058</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6577</v>
+        <v>3.5807</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6577</v>
+        <v>3.5807</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,44 +612,44 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6213</v>
+        <v>2.8146</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6213</v>
+        <v>2.8146</v>
       </c>
       <c r="N4" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.54</v>
+        <v>3.446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6962</v>
+        <v>0.6777</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9601</v>
+        <v>0.9445</v>
       </c>
       <c r="E5" t="n">
-        <v>3.54</v>
+        <v>3.446</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.54</v>
+        <v>3.446</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,19 +658,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.537</v>
+        <v>2.7088</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="M5" t="n">
-        <v>2.537</v>
+        <v>2.7088</v>
       </c>
       <c r="N5" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1989</v>
+        <v>3.3338</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6291</v>
+        <v>0.6556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8061</v>
+        <v>0.8934</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1989</v>
+        <v>3.3338</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1989</v>
+        <v>3.3338</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2925</v>
+        <v>2.6206</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2925</v>
+        <v>2.6206</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.125</v>
+        <v>2.1396</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4179</v>
+        <v>0.4208</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3213</v>
+        <v>0.3498</v>
       </c>
       <c r="E7" t="n">
-        <v>2.125</v>
+        <v>2.1396</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.125</v>
+        <v>2.1396</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5229</v>
+        <v>1.6819</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>186</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5229</v>
+        <v>1.6819</v>
       </c>
       <c r="N7" t="n">
         <v>186</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7929</v>
+        <v>1.824</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3526</v>
+        <v>0.3587</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1714</v>
+        <v>0.2061</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7929</v>
+        <v>1.824</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7929</v>
+        <v>1.824</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2849</v>
+        <v>1.4338</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>152</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2849</v>
+        <v>1.4338</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4065</v>
+        <v>1.422</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2766</v>
+        <v>0.2796</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.003</v>
+        <v>0.0231</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4065</v>
+        <v>1.422</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4065</v>
+        <v>1.422</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.008</v>
+        <v>1.1178</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>134</v>
       </c>
       <c r="M9" t="n">
-        <v>1.008</v>
+        <v>1.1178</v>
       </c>
       <c r="N9" t="n">
         <v>134</v>
@@ -860,26 +860,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>JBOEN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3868</v>
+        <v>1.4141</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2727</v>
+        <v>0.2781</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0119</v>
+        <v>0.0195</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3868</v>
+        <v>1.4141</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3868</v>
+        <v>1.4141</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9939</v>
+        <v>1.1116</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>134</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9939</v>
+        <v>1.1116</v>
       </c>
       <c r="N10" t="n">
         <v>134</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JBOEN</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3292</v>
+        <v>1.3771</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2614</v>
+        <v>0.2708</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0379</v>
+        <v>0.0027</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3292</v>
+        <v>1.3771</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3292</v>
+        <v>1.3771</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9526</v>
+        <v>1.0825</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>134</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9526</v>
+        <v>1.0825</v>
       </c>
       <c r="N11" t="n">
         <v>134</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1787</v>
+        <v>1.2246</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2318</v>
+        <v>0.2408</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1059</v>
+        <v>-0.0667</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1787</v>
+        <v>1.2246</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1787</v>
+        <v>1.2246</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8447</v>
+        <v>0.9626</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8447</v>
+        <v>0.9626</v>
       </c>
       <c r="N12" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1703</v>
+        <v>1.1835</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2301</v>
+        <v>0.2327</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1097</v>
+        <v>-0.0854</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1703</v>
+        <v>1.1835</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1703</v>
+        <v>1.1835</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8387</v>
+        <v>0.9303</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8387</v>
+        <v>0.9303</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0874</v>
+        <v>1.1094</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2138</v>
+        <v>0.2182</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1471</v>
+        <v>-0.1192</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0874</v>
+        <v>1.1094</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0874</v>
+        <v>1.1094</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7793</v>
+        <v>0.8721</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>69</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7793</v>
+        <v>0.8721</v>
       </c>
       <c r="N14" t="n">
         <v>69</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.997</v>
+        <v>1.0143</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1961</v>
+        <v>0.1995</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1879</v>
+        <v>-0.1625</v>
       </c>
       <c r="E15" t="n">
-        <v>0.997</v>
+        <v>1.0143</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.997</v>
+        <v>1.0143</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7145</v>
+        <v>0.7973</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>152</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7145</v>
+        <v>0.7973</v>
       </c>
       <c r="N15" t="n">
         <v>152</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9935</v>
+        <v>0.9564</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1954</v>
+        <v>0.1881</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1895</v>
+        <v>-0.1888</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9935</v>
+        <v>0.9564</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9935</v>
+        <v>0.9564</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.712</v>
+        <v>0.7518</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>134</v>
       </c>
       <c r="M16" t="n">
-        <v>0.712</v>
+        <v>0.7518</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9202</v>
+        <v>0.9423</v>
       </c>
       <c r="C17" t="n">
-        <v>0.181</v>
+        <v>0.1853</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2226</v>
+        <v>-0.1952</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9202</v>
+        <v>0.9423</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9202</v>
+        <v>0.9423</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6595</v>
+        <v>0.7407</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>89</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6595</v>
+        <v>0.7407</v>
       </c>
       <c r="N17" t="n">
         <v>89</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8001</v>
+        <v>0.8212</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1573</v>
+        <v>0.1615</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2768</v>
+        <v>-0.2504</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8001</v>
+        <v>0.8212</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8001</v>
+        <v>0.8212</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5734</v>
+        <v>0.6455</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5734</v>
+        <v>0.6455</v>
       </c>
       <c r="N18" t="n">
         <v>38</v>
@@ -1274,26 +1274,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6431</v>
+        <v>0.6842</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1265</v>
+        <v>0.1346</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3477</v>
+        <v>-0.3127</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6431</v>
+        <v>0.6842</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6431</v>
+        <v>0.6842</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4609</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4609</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5393</v>
+        <v>0.6725</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1061</v>
+        <v>0.1322</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3945</v>
+        <v>-0.3181</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5393</v>
+        <v>0.6725</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5393</v>
+        <v>0.6725</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3865</v>
+        <v>0.5286</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3865</v>
+        <v>0.5286</v>
       </c>
       <c r="N20" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.521</v>
+        <v>0.639</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1025</v>
+        <v>0.1257</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4028</v>
+        <v>-0.3333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.521</v>
+        <v>0.639</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.521</v>
+        <v>0.639</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3734</v>
+        <v>0.5023</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>186</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3734</v>
+        <v>0.5023</v>
       </c>
       <c r="N21" t="n">
         <v>186</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4806</v>
+        <v>0.5426</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0945</v>
+        <v>0.1067</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.421</v>
+        <v>-0.3772</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4806</v>
+        <v>0.5426</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4806</v>
+        <v>0.5426</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3444</v>
+        <v>0.4265</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>186</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3444</v>
+        <v>0.4265</v>
       </c>
       <c r="N22" t="n">
         <v>186</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4171</v>
+        <v>0.5109</v>
       </c>
       <c r="C23" t="n">
-        <v>0.082</v>
+        <v>0.1005</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4497</v>
+        <v>-0.3916</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4171</v>
+        <v>0.5109</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4171</v>
+        <v>0.5109</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2989</v>
+        <v>0.4016</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2989</v>
+        <v>0.4016</v>
       </c>
       <c r="N23" t="n">
-        <v>134</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3766</v>
+        <v>0.5094</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0741</v>
+        <v>0.1002</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.468</v>
+        <v>-0.3923</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3766</v>
+        <v>0.5094</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3766</v>
+        <v>0.5094</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2699</v>
+        <v>0.4004</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2699</v>
+        <v>0.4004</v>
       </c>
       <c r="N24" t="n">
-        <v>186</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3635</v>
+        <v>0.455</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0895</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4739</v>
+        <v>-0.4171</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3635</v>
+        <v>0.455</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3635</v>
+        <v>0.455</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2605</v>
+        <v>0.3577</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2605</v>
+        <v>0.3577</v>
       </c>
       <c r="N25" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tikuak</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3629</v>
+        <v>0.4371</v>
       </c>
       <c r="C26" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4742</v>
+        <v>-0.4252</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3629</v>
+        <v>0.4371</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3629</v>
+        <v>0.4371</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2601</v>
+        <v>0.3436</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2601</v>
+        <v>0.3436</v>
       </c>
       <c r="N26" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>tikuak</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3356</v>
+        <v>0.4048</v>
       </c>
       <c r="C27" t="n">
-        <v>0.066</v>
+        <v>0.0796</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4865</v>
+        <v>-0.4399</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3356</v>
+        <v>0.4048</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3356</v>
+        <v>0.4048</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2405</v>
+        <v>0.3182</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>69</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2405</v>
+        <v>0.3182</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3275</v>
+        <v>0.4002</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0644</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4902</v>
+        <v>-0.442</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3275</v>
+        <v>0.4002</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3275</v>
+        <v>0.4002</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,19 +1716,19 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2347</v>
+        <v>0.3146</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2347</v>
+        <v>0.3146</v>
       </c>
       <c r="N28" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3144</v>
+        <v>0.3474</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0618</v>
+        <v>0.0683</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4961</v>
+        <v>-0.4661</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3144</v>
+        <v>0.3474</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3144</v>
+        <v>0.3474</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2253</v>
+        <v>0.2731</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>79</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2253</v>
+        <v>0.2731</v>
       </c>
       <c r="N29" t="n">
         <v>79</v>
@@ -1780,26 +1780,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.284</v>
+        <v>0.2837</v>
       </c>
       <c r="C30" t="n">
         <v>0.0558</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5098</v>
+        <v>-0.4951</v>
       </c>
       <c r="E30" t="n">
-        <v>0.284</v>
+        <v>0.2837</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.284</v>
+        <v>0.2837</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2035</v>
+        <v>0.223</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2035</v>
+        <v>0.223</v>
       </c>
       <c r="N30" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.26</v>
+        <v>0.2312</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0511</v>
+        <v>0.0455</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5206</v>
+        <v>-0.519</v>
       </c>
       <c r="E31" t="n">
-        <v>0.26</v>
+        <v>0.2312</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.26</v>
+        <v>0.2312</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1863</v>
+        <v>0.1817</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1863</v>
+        <v>0.1817</v>
       </c>
       <c r="N31" t="n">
         <v>69</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2196</v>
+        <v>0.209</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0432</v>
+        <v>0.0411</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5389</v>
+        <v>-0.5291</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2196</v>
+        <v>0.209</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2196</v>
+        <v>0.209</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1574</v>
+        <v>0.1643</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>89</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1574</v>
+        <v>0.1643</v>
       </c>
       <c r="N32" t="n">
         <v>89</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0579</v>
+        <v>0.1024</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0114</v>
+        <v>0.0201</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6119</v>
+        <v>-0.5776</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0579</v>
+        <v>0.1024</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0579</v>
+        <v>0.1024</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0415</v>
+        <v>0.0805</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>79</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0415</v>
+        <v>0.0805</v>
       </c>
       <c r="N33" t="n">
         <v>79</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0105</v>
+        <v>0.0318</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0021</v>
+        <v>0.0063</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6428</v>
+        <v>-0.6097</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0105</v>
+        <v>0.0318</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0105</v>
+        <v>0.0318</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0075</v>
+        <v>0.025</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0075</v>
+        <v>0.025</v>
       </c>
       <c r="N34" t="n">
         <v>69</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0324</v>
+        <v>-0.0197</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0064</v>
+        <v>-0.0039</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6526</v>
+        <v>-0.6332</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0324</v>
+        <v>-0.0197</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0324</v>
+        <v>-0.0197</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0232</v>
+        <v>-0.0155</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0232</v>
+        <v>-0.0155</v>
       </c>
       <c r="N35" t="n">
         <v>38</v>
@@ -2056,26 +2056,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2876</v>
+        <v>-0.229</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0566</v>
+        <v>-0.045</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7679</v>
+        <v>-0.7284</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2876</v>
+        <v>-0.229</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2876</v>
+        <v>-0.229</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,44 +2084,44 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2061</v>
+        <v>-0.18</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.2061</v>
+        <v>-0.18</v>
       </c>
       <c r="N36" t="n">
-        <v>79</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2891</v>
+        <v>-0.2791</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0569</v>
+        <v>-0.0549</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7685</v>
+        <v>-0.7513</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2891</v>
+        <v>-0.2791</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2891</v>
+        <v>-0.2791</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2072</v>
+        <v>-0.2194</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.2072</v>
+        <v>-0.2194</v>
       </c>
       <c r="N37" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7186</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1413</v>
+        <v>-0.1345</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9624</v>
+        <v>-0.9356</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7186</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7186</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.515</v>
+        <v>-0.5377</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>89</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.515</v>
+        <v>-0.5377</v>
       </c>
       <c r="N38" t="n">
         <v>89</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7518</v>
+        <v>-0.7307</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1478</v>
+        <v>-0.1437</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9774</v>
+        <v>-0.9568</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7518</v>
+        <v>-0.7307</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7518</v>
+        <v>-0.7307</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5744</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>69</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.5744</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.8855</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1741</v>
+        <v>-0.1656</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0378</v>
+        <v>-1.0076</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8855</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8855</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.662</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.662</v>
       </c>
       <c r="N40" t="n">
         <v>38</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.296</v>
+        <v>-1.2036</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2549</v>
+        <v>-0.2367</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2231</v>
+        <v>-1.1721</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.296</v>
+        <v>-1.2036</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.296</v>
+        <v>-1.2036</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9288</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9288</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>38</v>
@@ -2429,10 +2429,10 @@
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.275</v>
+        <v>0.2686</v>
       </c>
       <c r="J2" t="n">
-        <v>5.775</v>
+        <v>5.6406</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1082</v>
+        <v>-0.1241</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.2722</v>
+        <v>-2.6061</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1814</v>
+        <v>-0.1989</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.8094</v>
+        <v>-4.1769</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2601</v>
+        <v>-0.277</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.4621</v>
+        <v>-5.817</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3557</v>
+        <v>-0.3698</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.4697</v>
+        <v>-7.7658</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6242</v>
+        <v>1.7577</v>
       </c>
       <c r="J7" t="n">
-        <v>34.1082</v>
+        <v>36.9117</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0215</v>
+        <v>0.9735</v>
       </c>
       <c r="J8" t="n">
-        <v>21.4515</v>
+        <v>20.4435</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3964</v>
+        <v>0.3998</v>
       </c>
       <c r="J9" t="n">
-        <v>8.324400000000001</v>
+        <v>8.395799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2079</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5587</v>
+        <v>-0.5182</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.7327</v>
+        <v>-10.8822</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0963</v>
+        <v>-0.1203</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6371</v>
+        <v>-2.0451</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0963</v>
+        <v>-0.1203</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6371</v>
+        <v>-2.0451</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4059</v>
+        <v>-0.422</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.9003</v>
+        <v>-7.174</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.434</v>
+        <v>-0.4485</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.378</v>
+        <v>-7.6245</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4527</v>
+        <v>-0.4661</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.6959</v>
+        <v>-7.9237</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5262</v>
+        <v>1.6613</v>
       </c>
       <c r="J17" t="n">
-        <v>25.9454</v>
+        <v>28.2421</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4339</v>
+        <v>1.558</v>
       </c>
       <c r="J18" t="n">
-        <v>24.3763</v>
+        <v>26.486</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7992</v>
+        <v>0.7657</v>
       </c>
       <c r="J19" t="n">
-        <v>13.5864</v>
+        <v>13.0169</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3647</v>
+        <v>0.3777</v>
       </c>
       <c r="J20" t="n">
-        <v>6.1999</v>
+        <v>6.4209</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3299</v>
+        <v>-0.301</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.6083</v>
+        <v>-5.117</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4922</v>
+        <v>0.4993</v>
       </c>
       <c r="J22" t="n">
-        <v>10.8284</v>
+        <v>10.9846</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4102</v>
+        <v>0.4216</v>
       </c>
       <c r="J23" t="n">
-        <v>9.0244</v>
+        <v>9.2752</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0853</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8766</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0121</v>
+        <v>0.0212</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2662</v>
+        <v>0.4664</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.92</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1255</v>
+        <v>-0.1344</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.761</v>
+        <v>-2.9568</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2982</v>
+        <v>0.2999</v>
       </c>
       <c r="J27" t="n">
-        <v>6.5604</v>
+        <v>6.5978</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1028</v>
+        <v>0.108</v>
       </c>
       <c r="J28" t="n">
-        <v>2.2616</v>
+        <v>2.376</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.5366</v>
+        <v>-2.849</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2398</v>
+        <v>-0.2551</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.2756</v>
+        <v>-5.6122</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3081</v>
+        <v>-0.322</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.7782</v>
+        <v>-7.084</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6845</v>
+        <v>0.6587</v>
       </c>
       <c r="J32" t="n">
-        <v>15.7435</v>
+        <v>15.1501</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0046</v>
+        <v>-0.0023</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1121</v>
+        <v>-0.124</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.5783</v>
+        <v>-2.852</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1347</v>
+        <v>-0.1473</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.0981</v>
+        <v>-3.3879</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1779</v>
+        <v>-0.1913</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.0917</v>
+        <v>-4.3999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0417</v>
+        <v>0.9909</v>
       </c>
       <c r="J37" t="n">
-        <v>23.9591</v>
+        <v>22.7907</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8415</v>
+        <v>0.7905</v>
       </c>
       <c r="J38" t="n">
-        <v>19.3545</v>
+        <v>18.1815</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.98</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1251</v>
+        <v>-0.1212</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.8773</v>
+        <v>-2.7876</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.98</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1251</v>
+        <v>-0.1212</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.8773</v>
+        <v>-2.7876</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2629</v>
+        <v>-0.2539</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.0467</v>
+        <v>-5.8397</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4767</v>
+        <v>0.5442</v>
       </c>
       <c r="J42" t="n">
-        <v>9.0573</v>
+        <v>10.3398</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4376</v>
+        <v>0.498</v>
       </c>
       <c r="J43" t="n">
-        <v>8.314399999999999</v>
+        <v>9.462</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3428</v>
+        <v>0.3667</v>
       </c>
       <c r="J44" t="n">
-        <v>6.5132</v>
+        <v>6.9673</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2308</v>
+        <v>0.2492</v>
       </c>
       <c r="J45" t="n">
-        <v>4.3852</v>
+        <v>4.7348</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2515</v>
+        <v>-0.2601</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.7785</v>
+        <v>-4.9419</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3362</v>
+        <v>0.341</v>
       </c>
       <c r="J47" t="n">
-        <v>6.3878</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04</v>
+        <v>0.0421</v>
       </c>
       <c r="J48" t="n">
-        <v>0.76</v>
+        <v>0.7999000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0936</v>
+        <v>-0.1066</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.7784</v>
+        <v>-2.0254</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.77</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2601</v>
+        <v>-0.275</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.9419</v>
+        <v>-5.225</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2893</v>
+        <v>-0.3036</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.4967</v>
+        <v>-5.7684</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4617</v>
+        <v>0.5084</v>
       </c>
       <c r="J52" t="n">
-        <v>10.1574</v>
+        <v>11.1848</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3851</v>
+        <v>0.4127</v>
       </c>
       <c r="J53" t="n">
-        <v>8.472200000000001</v>
+        <v>9.0794</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1171</v>
+        <v>-0.1309</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.5762</v>
+        <v>-2.8798</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.301</v>
+        <v>-0.3146</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.622</v>
+        <v>-6.9212</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3768</v>
+        <v>-0.388</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.2896</v>
+        <v>-8.536</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.3</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6178</v>
+        <v>0.6825</v>
       </c>
       <c r="J57" t="n">
-        <v>13.5916</v>
+        <v>15.015</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5476</v>
+        <v>0.6049</v>
       </c>
       <c r="J58" t="n">
-        <v>12.0472</v>
+        <v>13.3078</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3565</v>
+        <v>0.3709</v>
       </c>
       <c r="J59" t="n">
-        <v>7.843</v>
+        <v>8.159800000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1366</v>
+        <v>0.1499</v>
       </c>
       <c r="J60" t="n">
-        <v>3.0052</v>
+        <v>3.2978</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2645</v>
+        <v>-0.2551</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.819</v>
+        <v>-5.6122</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4162</v>
+        <v>0.4502</v>
       </c>
       <c r="J62" t="n">
-        <v>9.1564</v>
+        <v>9.904400000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1535</v>
+        <v>0.1518</v>
       </c>
       <c r="J63" t="n">
-        <v>3.377</v>
+        <v>3.3396</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.78</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.3306</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3576</v>
+        <v>-0.3713</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.8672</v>
+        <v>-8.1686</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3576</v>
+        <v>-0.3713</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.8672</v>
+        <v>-8.1686</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0781</v>
+        <v>1.1816</v>
       </c>
       <c r="J67" t="n">
-        <v>23.7182</v>
+        <v>25.9952</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.33</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6431</v>
+        <v>0.7138</v>
       </c>
       <c r="J68" t="n">
-        <v>14.1482</v>
+        <v>15.7036</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6163</v>
+        <v>0.6843</v>
       </c>
       <c r="J69" t="n">
-        <v>13.5586</v>
+        <v>15.0546</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2711</v>
+        <v>0.2818</v>
       </c>
       <c r="J70" t="n">
-        <v>5.9642</v>
+        <v>6.1996</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.023</v>
+        <v>-0.9302</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.506</v>
+        <v>-20.4644</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2166</v>
+        <v>0.2102</v>
       </c>
       <c r="J72" t="n">
-        <v>4.1154</v>
+        <v>3.9938</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1679</v>
+        <v>0.1623</v>
       </c>
       <c r="J73" t="n">
-        <v>3.1901</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0443</v>
+        <v>0.0321</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8417</v>
+        <v>0.6099</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.54</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4645</v>
+        <v>-0.474</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.8255</v>
+        <v>-9.006</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4921</v>
+        <v>-0.5</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.3499</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9354</v>
+        <v>1.0333</v>
       </c>
       <c r="J77" t="n">
-        <v>17.7726</v>
+        <v>19.6327</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.53</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8859</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>16.8321</v>
+        <v>18.6257</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4863</v>
+        <v>0.5414</v>
       </c>
       <c r="J79" t="n">
-        <v>9.239699999999999</v>
+        <v>10.2866</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2532</v>
+        <v>0.2693</v>
       </c>
       <c r="J80" t="n">
-        <v>4.8108</v>
+        <v>5.1167</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0631</v>
+        <v>0.0892</v>
       </c>
       <c r="J81" t="n">
-        <v>1.1989</v>
+        <v>1.6948</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.401</v>
+        <v>0.451</v>
       </c>
       <c r="J82" t="n">
-        <v>8.821999999999999</v>
+        <v>9.922000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3351</v>
+        <v>0.3535</v>
       </c>
       <c r="J83" t="n">
-        <v>7.3722</v>
+        <v>7.777</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2777</v>
+        <v>0.2932</v>
       </c>
       <c r="J84" t="n">
-        <v>6.1094</v>
+        <v>6.4504</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1004</v>
       </c>
       <c r="J85" t="n">
-        <v>1.903</v>
+        <v>2.2088</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.262</v>
+        <v>-0.2725</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.764</v>
+        <v>-5.995</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.186</v>
+        <v>0.192</v>
       </c>
       <c r="J87" t="n">
-        <v>4.092</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1357</v>
+        <v>0.1421</v>
       </c>
       <c r="J88" t="n">
-        <v>2.9854</v>
+        <v>3.1262</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1357</v>
+        <v>0.1421</v>
       </c>
       <c r="J89" t="n">
-        <v>2.9854</v>
+        <v>3.1262</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2216</v>
+        <v>-0.2367</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.8752</v>
+        <v>-5.2074</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3573</v>
+        <v>-0.3694</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.8606</v>
+        <v>-8.126799999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4229</v>
+        <v>0.4676</v>
       </c>
       <c r="J92" t="n">
-        <v>10.1496</v>
+        <v>11.2224</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3178</v>
+        <v>0.323</v>
       </c>
       <c r="J93" t="n">
-        <v>7.6272</v>
+        <v>7.752</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.04</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1118</v>
+        <v>0.1215</v>
       </c>
       <c r="J94" t="n">
-        <v>2.6832</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1591</v>
+        <v>-0.1716</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.8184</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2013</v>
+        <v>-0.2142</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.8312</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8736</v>
+        <v>0.9524</v>
       </c>
       <c r="J97" t="n">
-        <v>20.9664</v>
+        <v>22.8576</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5006</v>
+        <v>0.5463</v>
       </c>
       <c r="J98" t="n">
-        <v>12.0144</v>
+        <v>13.1112</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4366</v>
+        <v>-0.4214</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.4784</v>
+        <v>-10.1136</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6758</v>
+        <v>-0.6353</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.2192</v>
+        <v>-15.2472</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7773</v>
+        <v>-0.7245</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.6552</v>
+        <v>-17.388</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6468</v>
       </c>
       <c r="J102" t="n">
-        <v>13.064</v>
+        <v>14.8764</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3399</v>
+        <v>0.3585</v>
       </c>
       <c r="J103" t="n">
-        <v>7.8177</v>
+        <v>8.2455</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0745</v>
+        <v>0.0866</v>
       </c>
       <c r="J104" t="n">
-        <v>1.7135</v>
+        <v>1.9918</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2381</v>
+        <v>-0.2496</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.4763</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2973</v>
+        <v>-0.308</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.8379</v>
+        <v>-7.084</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4788</v>
+        <v>0.5334</v>
       </c>
       <c r="J107" t="n">
-        <v>11.0124</v>
+        <v>12.2682</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0138</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.7273</v>
+        <v>-1.9665</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2179</v>
+        <v>-0.2317</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.0117</v>
+        <v>-5.3291</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.228</v>
+        <v>-0.2417</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.244</v>
+        <v>-5.5591</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6494</v>
+        <v>0.7275</v>
       </c>
       <c r="J112" t="n">
-        <v>23.3784</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1911</v>
+        <v>0.2026</v>
       </c>
       <c r="J113" t="n">
-        <v>6.8796</v>
+        <v>7.2936</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0068</v>
+        <v>-0.0052</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.2448</v>
+        <v>-0.1872</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0068</v>
+        <v>-0.0052</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.2448</v>
+        <v>-0.1872</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.85</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1969</v>
+        <v>-0.2085</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.0884</v>
+        <v>-7.506</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.61</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0266</v>
+        <v>1.123</v>
       </c>
       <c r="J117" t="n">
-        <v>36.9576</v>
+        <v>40.428</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.15</v>
       </c>
       <c r="I118" t="n">
-        <v>0.401</v>
+        <v>0.4377</v>
       </c>
       <c r="J118" t="n">
-        <v>14.436</v>
+        <v>15.7572</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3713</v>
+        <v>0.3943</v>
       </c>
       <c r="J119" t="n">
-        <v>13.3668</v>
+        <v>14.1948</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2974</v>
+        <v>-0.2855</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.7064</v>
+        <v>-10.278</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.86</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4996</v>
+        <v>-0.4712</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.9856</v>
+        <v>-16.9632</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.12</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2835</v>
+        <v>0.2887</v>
       </c>
       <c r="J122" t="n">
-        <v>8.505000000000001</v>
+        <v>8.661</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2636</v>
+        <v>0.2697</v>
       </c>
       <c r="J123" t="n">
-        <v>7.908</v>
+        <v>8.090999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2435</v>
+        <v>0.2504</v>
       </c>
       <c r="J124" t="n">
-        <v>7.305</v>
+        <v>7.512</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0644</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.932</v>
+        <v>-2.202</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2701</v>
+        <v>-0.2829</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.103</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5857</v>
+        <v>0.6449</v>
       </c>
       <c r="J127" t="n">
-        <v>17.571</v>
+        <v>19.347</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4081</v>
+        <v>0.4446</v>
       </c>
       <c r="J128" t="n">
-        <v>12.243</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1802</v>
+        <v>0.1888</v>
       </c>
       <c r="J129" t="n">
-        <v>5.406</v>
+        <v>5.664</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1133</v>
+        <v>0.1241</v>
       </c>
       <c r="J130" t="n">
-        <v>3.399</v>
+        <v>3.723</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3137</v>
+        <v>-0.3041</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.411</v>
+        <v>-9.122999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7842</v>
+        <v>0.8656</v>
       </c>
       <c r="J132" t="n">
-        <v>21.9576</v>
+        <v>24.2368</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5962</v>
+        <v>0.6604</v>
       </c>
       <c r="J133" t="n">
-        <v>16.6936</v>
+        <v>18.4912</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.2</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4701</v>
+        <v>0.5198</v>
       </c>
       <c r="J134" t="n">
-        <v>13.1628</v>
+        <v>14.5544</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.092</v>
+        <v>0.1094</v>
       </c>
       <c r="J135" t="n">
-        <v>2.576</v>
+        <v>3.0632</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3959</v>
+        <v>-0.3748</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.0852</v>
+        <v>-10.4944</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1608</v>
+        <v>0.1634</v>
       </c>
       <c r="J137" t="n">
-        <v>4.5024</v>
+        <v>4.5752</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1368</v>
+        <v>0.1396</v>
       </c>
       <c r="J138" t="n">
-        <v>3.8304</v>
+        <v>3.9088</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0555</v>
+        <v>0.0561</v>
       </c>
       <c r="J139" t="n">
-        <v>1.554</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2487</v>
+        <v>-0.2641</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.9636</v>
+        <v>-7.3948</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3262</v>
+        <v>-0.3398</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.133599999999999</v>
+        <v>-9.5144</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.28</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4202</v>
+        <v>0.461</v>
       </c>
       <c r="J142" t="n">
-        <v>8.404</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1963</v>
+        <v>-0.2126</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.926</v>
+        <v>-4.252</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2064</v>
+        <v>-0.2227</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.128</v>
+        <v>-4.454</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2363</v>
+        <v>-0.2524</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.726</v>
+        <v>-5.048</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2658</v>
+        <v>-0.2814</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.316</v>
+        <v>-5.628</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.68</v>
       </c>
       <c r="I147" t="n">
-        <v>0.608</v>
+        <v>0.6986</v>
       </c>
       <c r="J147" t="n">
-        <v>12.16</v>
+        <v>13.972</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.46</v>
       </c>
       <c r="I148" t="n">
-        <v>0.471</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>9.42</v>
+        <v>10.776</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.4</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4326</v>
+        <v>0.4932</v>
       </c>
       <c r="J149" t="n">
-        <v>8.651999999999999</v>
+        <v>9.864000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1033</v>
+        <v>-0.1074</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.066</v>
+        <v>-2.148</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.184</v>
+        <v>-0.1911</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.68</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0201</v>
+        <v>1.1194</v>
       </c>
       <c r="J152" t="n">
-        <v>21.4221</v>
+        <v>23.5074</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.14</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3797</v>
+        <v>0.4098</v>
       </c>
       <c r="J153" t="n">
-        <v>7.9737</v>
+        <v>8.6058</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3029</v>
+        <v>0.3106</v>
       </c>
       <c r="J154" t="n">
-        <v>6.3609</v>
+        <v>6.5226</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.08</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2453</v>
+        <v>0.257</v>
       </c>
       <c r="J155" t="n">
-        <v>5.1513</v>
+        <v>5.397</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1528</v>
+        <v>0.1698</v>
       </c>
       <c r="J156" t="n">
-        <v>3.2088</v>
+        <v>3.5658</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2335</v>
+        <v>0.2332</v>
       </c>
       <c r="J157" t="n">
-        <v>4.9035</v>
+        <v>4.8972</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1158</v>
+        <v>0.1174</v>
       </c>
       <c r="J158" t="n">
-        <v>2.4318</v>
+        <v>2.4654</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1139</v>
+        <v>-0.1284</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.3919</v>
+        <v>-2.6964</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1868</v>
+        <v>-0.2029</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.9228</v>
+        <v>-4.2609</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3717</v>
+        <v>-0.384</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.8057</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.39</v>
       </c>
       <c r="I162" t="n">
-        <v>0.445</v>
+        <v>0.5036</v>
       </c>
       <c r="J162" t="n">
-        <v>10.235</v>
+        <v>11.5828</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2029</v>
+        <v>0.2186</v>
       </c>
       <c r="J163" t="n">
-        <v>4.6667</v>
+        <v>5.0278</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.04</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0726</v>
+        <v>0.0852</v>
       </c>
       <c r="J164" t="n">
-        <v>1.6698</v>
+        <v>1.9596</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.99</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0297</v>
+        <v>-0.0322</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.6831</v>
+        <v>-0.7406</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0985</v>
+        <v>-0.107</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.2655</v>
+        <v>-2.461</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3706</v>
+        <v>0.3931</v>
       </c>
       <c r="J167" t="n">
-        <v>8.5238</v>
+        <v>9.0413</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3447</v>
+        <v>0.3529</v>
       </c>
       <c r="J168" t="n">
-        <v>7.9281</v>
+        <v>8.1167</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.1786</v>
+        <v>-3.5144</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.1786</v>
+        <v>-3.5144</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.47</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5401</v>
+        <v>-0.5434</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.4223</v>
+        <v>-12.4982</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.37</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5553</v>
+        <v>0.6212</v>
       </c>
       <c r="J172" t="n">
-        <v>22.212</v>
+        <v>24.848</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.33</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5161</v>
+        <v>0.5766</v>
       </c>
       <c r="J173" t="n">
-        <v>20.644</v>
+        <v>23.064</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1062</v>
+        <v>0.1176</v>
       </c>
       <c r="J174" t="n">
-        <v>4.248</v>
+        <v>4.704</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.84</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2064</v>
+        <v>-0.2182</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.256</v>
+        <v>-8.728</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.78</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2669</v>
+        <v>-0.2784</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.676</v>
+        <v>-11.136</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9947</v>
+        <v>1.0903</v>
       </c>
       <c r="J177" t="n">
-        <v>39.788</v>
+        <v>43.612</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.443</v>
+        <v>0.4886</v>
       </c>
       <c r="J178" t="n">
-        <v>17.72</v>
+        <v>19.544</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3536</v>
+        <v>0.3677</v>
       </c>
       <c r="J179" t="n">
-        <v>14.144</v>
+        <v>14.708</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3121</v>
+        <v>0.3172</v>
       </c>
       <c r="J180" t="n">
-        <v>12.484</v>
+        <v>12.688</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6901</v>
+        <v>-0.6407</v>
       </c>
       <c r="J181" t="n">
-        <v>-27.604</v>
+        <v>-25.628</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6552</v>
+        <v>0.7218</v>
       </c>
       <c r="J182" t="n">
-        <v>10.4832</v>
+        <v>11.5488</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2026</v>
+        <v>-0.2198</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.2416</v>
+        <v>-3.5168</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2907</v>
+        <v>-0.3066</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.6512</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3003</v>
+        <v>-0.3159</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.8048</v>
+        <v>-5.0544</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3761</v>
+        <v>-0.3891</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.0176</v>
+        <v>-6.2256</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.5161</v>
+        <v>1.649</v>
       </c>
       <c r="J187" t="n">
-        <v>24.2576</v>
+        <v>26.384</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.32</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6092</v>
+        <v>0.6815</v>
       </c>
       <c r="J188" t="n">
-        <v>9.747199999999999</v>
+        <v>10.904</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5961</v>
+        <v>0.6669</v>
       </c>
       <c r="J189" t="n">
-        <v>9.537599999999999</v>
+        <v>10.6704</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4439</v>
+        <v>0.4972</v>
       </c>
       <c r="J190" t="n">
-        <v>7.1024</v>
+        <v>7.9552</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1691</v>
+        <v>0.1966</v>
       </c>
       <c r="J191" t="n">
-        <v>2.7056</v>
+        <v>3.1456</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8363</v>
+        <v>0.9267</v>
       </c>
       <c r="J192" t="n">
-        <v>16.726</v>
+        <v>18.534</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.06</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1779</v>
+        <v>0.1818</v>
       </c>
       <c r="J193" t="n">
-        <v>3.558</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2112</v>
+        <v>-0.2264</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.224</v>
+        <v>-4.528</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.413</v>
+        <v>-0.4229</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.26</v>
+        <v>-8.458</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4498</v>
+        <v>-0.4579</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.996</v>
+        <v>-9.157999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2895</v>
+        <v>1.407</v>
       </c>
       <c r="J197" t="n">
-        <v>25.79</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.699</v>
+        <v>0.7773</v>
       </c>
       <c r="J198" t="n">
-        <v>13.98</v>
+        <v>15.546</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4598</v>
+        <v>0.511</v>
       </c>
       <c r="J199" t="n">
-        <v>9.196</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.01</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.0113</v>
+        <v>0.0139</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.226</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3916</v>
+        <v>-0.3654</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.832</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3898</v>
+        <v>0.4074</v>
       </c>
       <c r="J202" t="n">
-        <v>7.0164</v>
+        <v>7.3332</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0568</v>
+        <v>0.0412</v>
       </c>
       <c r="J203" t="n">
-        <v>1.0224</v>
+        <v>0.7416</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2629</v>
+        <v>-0.2812</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.7322</v>
+        <v>-5.0616</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.58</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4234</v>
+        <v>-0.4356</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.6212</v>
+        <v>-7.8408</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.479</v>
+        <v>-0.4882</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.622</v>
+        <v>-8.787599999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.2</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6661</v>
+        <v>1.8005</v>
       </c>
       <c r="J207" t="n">
-        <v>29.9898</v>
+        <v>32.409</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.41</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7302</v>
+        <v>0.8129</v>
       </c>
       <c r="J208" t="n">
-        <v>13.1436</v>
+        <v>14.6322</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.09</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2458</v>
+        <v>0.2642</v>
       </c>
       <c r="J209" t="n">
-        <v>4.4244</v>
+        <v>4.7556</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1323</v>
+        <v>-0.1136</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.3814</v>
+        <v>-2.0448</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4024</v>
+        <v>-0.373</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.2432</v>
+        <v>-6.714</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8247/event_8247_evp_summary.xlsx
+++ b/database/event/8247/event_8247_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.637</v>
+        <v>7.7415</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5018</v>
+        <v>1.5224</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8523</v>
+        <v>2.8441</v>
       </c>
       <c r="E2" t="n">
-        <v>7.637</v>
+        <v>7.7415</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5078</v>
+        <v>5.7355</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0831</v>
+        <v>1.1279</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8831</v>
+        <v>1.9481</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5078</v>
+        <v>5.7355</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5807</v>
+        <v>3.7617</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7042</v>
+        <v>0.7398</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0058</v>
+        <v>1.0664</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5807</v>
+        <v>3.7617</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -630,26 +630,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.446</v>
+        <v>3.4405</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6777</v>
+        <v>0.6766</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9445</v>
+        <v>0.923</v>
       </c>
       <c r="E5" t="n">
-        <v>3.446</v>
+        <v>3.4405</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.446</v>
+        <v>3.3338</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7088</v>
+        <v>2.6206</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>225</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7088</v>
+        <v>2.6206</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -676,26 +676,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3338</v>
+        <v>3.4205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6556</v>
+        <v>0.6727</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8934</v>
+        <v>0.914</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3338</v>
+        <v>3.4205</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3338</v>
+        <v>3.446</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6206</v>
+        <v>2.7088</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6206</v>
+        <v>2.7088</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.1396</v>
+        <v>2.194</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4208</v>
+        <v>0.4315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3498</v>
+        <v>0.3662</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1396</v>
+        <v>2.194</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.824</v>
+        <v>1.7956</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3587</v>
+        <v>0.3531</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2061</v>
+        <v>0.1882</v>
       </c>
       <c r="E8" t="n">
-        <v>1.824</v>
+        <v>1.7956</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>JBOEN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.422</v>
+        <v>1.5561</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2796</v>
+        <v>0.306</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0231</v>
+        <v>0.0813</v>
       </c>
       <c r="E9" t="n">
-        <v>1.422</v>
+        <v>1.5561</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.422</v>
+        <v>1.4141</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1178</v>
+        <v>1.1116</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>134</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1178</v>
+        <v>1.1116</v>
       </c>
       <c r="N9" t="n">
         <v>134</v>
@@ -860,26 +860,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JBOEN</t>
+          <t>Jorko</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4141</v>
+        <v>1.4588</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2781</v>
+        <v>0.2869</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0195</v>
+        <v>0.0378</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4141</v>
+        <v>1.4588</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4141</v>
+        <v>0.8212</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,19 +888,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1116</v>
+        <v>0.6455</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1116</v>
+        <v>0.6455</v>
       </c>
       <c r="N10" t="n">
-        <v>134</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3771</v>
+        <v>1.404</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2708</v>
+        <v>0.2761</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0027</v>
+        <v>0.0133</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3771</v>
+        <v>1.404</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2246</v>
+        <v>1.3459</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2408</v>
+        <v>0.2647</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0667</v>
+        <v>-0.0126</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2246</v>
+        <v>1.3459</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2246</v>
+        <v>1.1094</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9626</v>
+        <v>0.8721</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9626</v>
+        <v>0.8721</v>
       </c>
       <c r="N12" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1835</v>
+        <v>1.295</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2327</v>
+        <v>0.2547</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0854</v>
+        <v>-0.0354</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1835</v>
+        <v>1.295</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1835</v>
+        <v>1.2246</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9303</v>
+        <v>0.9626</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9303</v>
+        <v>0.9626</v>
       </c>
       <c r="N13" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1094</v>
+        <v>1.2864</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2182</v>
+        <v>0.253</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1192</v>
+        <v>-0.0392</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1094</v>
+        <v>1.2864</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1094</v>
+        <v>1.1835</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8721</v>
+        <v>0.9303</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8721</v>
+        <v>0.9303</v>
       </c>
       <c r="N14" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0143</v>
+        <v>1.244</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1995</v>
+        <v>0.2446</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1625</v>
+        <v>-0.0582</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0143</v>
+        <v>1.244</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0143</v>
+        <v>1.422</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7973</v>
+        <v>1.1178</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7973</v>
+        <v>1.1178</v>
       </c>
       <c r="N15" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9564</v>
+        <v>1.03</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1881</v>
+        <v>0.2026</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1888</v>
+        <v>-0.1537</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9564</v>
+        <v>1.03</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9564</v>
+        <v>0.9423</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7518</v>
+        <v>0.7407</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7518</v>
+        <v>0.7407</v>
       </c>
       <c r="N16" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9423</v>
+        <v>0.9826</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1853</v>
+        <v>0.1932</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1952</v>
+        <v>-0.1749</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9423</v>
+        <v>0.9826</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9423</v>
+        <v>1.0143</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7407</v>
+        <v>0.7973</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7407</v>
+        <v>0.7973</v>
       </c>
       <c r="N17" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jorko</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8212</v>
+        <v>0.9313</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1615</v>
+        <v>0.1831</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2504</v>
+        <v>-0.1978</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8212</v>
+        <v>0.9313</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8212</v>
+        <v>0.9564</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6455</v>
+        <v>0.7518</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6455</v>
+        <v>0.7518</v>
       </c>
       <c r="N18" t="n">
-        <v>38</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6842</v>
+        <v>0.6953</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1346</v>
+        <v>0.1367</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3127</v>
+        <v>-0.3032</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6842</v>
+        <v>0.6953</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6842</v>
+        <v>0.6725</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5286</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5286</v>
       </c>
       <c r="N19" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6725</v>
+        <v>0.612</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1322</v>
+        <v>0.1204</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3181</v>
+        <v>-0.3405</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6725</v>
+        <v>0.612</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6725</v>
+        <v>0.455</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,19 +1348,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5286</v>
+        <v>0.3577</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5286</v>
+        <v>0.3577</v>
       </c>
       <c r="N20" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.639</v>
+        <v>0.5976</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1257</v>
+        <v>0.1175</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3333</v>
+        <v>-0.3469</v>
       </c>
       <c r="E21" t="n">
-        <v>0.639</v>
+        <v>0.5976</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5426</v>
+        <v>0.5084</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1067</v>
+        <v>0.1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3772</v>
+        <v>-0.3867</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5426</v>
+        <v>0.5084</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5109</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1005</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3916</v>
+        <v>-0.3898</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5109</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5109</v>
+        <v>0.6842</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,19 +1486,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4016</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4016</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>225</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5094</v>
+        <v>0.4898</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1002</v>
+        <v>0.0963</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3923</v>
+        <v>-0.395</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5094</v>
+        <v>0.4898</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1550,26 +1550,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.455</v>
+        <v>0.4733</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0895</v>
+        <v>0.0931</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4171</v>
+        <v>-0.4024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.455</v>
+        <v>0.4733</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.455</v>
+        <v>0.5109</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3577</v>
+        <v>0.4016</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3577</v>
+        <v>0.4016</v>
       </c>
       <c r="N25" t="n">
-        <v>134</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4371</v>
+        <v>0.4196</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4252</v>
+        <v>-0.4264</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4371</v>
+        <v>0.4196</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4371</v>
+        <v>0.3474</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3436</v>
+        <v>0.2731</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3436</v>
+        <v>0.2731</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tikuak</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4048</v>
+        <v>0.3958</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0796</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4399</v>
+        <v>-0.437</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4048</v>
+        <v>0.3958</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4048</v>
+        <v>0.2837</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3182</v>
+        <v>0.223</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3182</v>
+        <v>0.223</v>
       </c>
       <c r="N27" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>tikuak</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4002</v>
+        <v>0.3896</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0766</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.442</v>
+        <v>-0.4398</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4002</v>
+        <v>0.3896</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4002</v>
+        <v>0.4048</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3146</v>
+        <v>0.3182</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3146</v>
+        <v>0.3182</v>
       </c>
       <c r="N28" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>DarkMeister</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3474</v>
+        <v>0.3555</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0683</v>
+        <v>0.0699</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4661</v>
+        <v>-0.455</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3474</v>
+        <v>0.3555</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3474</v>
+        <v>0.2312</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2731</v>
+        <v>0.1817</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2731</v>
+        <v>0.1817</v>
       </c>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2837</v>
+        <v>0.3544</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0558</v>
+        <v>0.0697</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4951</v>
+        <v>-0.4555</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2837</v>
+        <v>0.3544</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2837</v>
+        <v>0.4002</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.223</v>
+        <v>0.3146</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="M30" t="n">
-        <v>0.223</v>
+        <v>0.3146</v>
       </c>
       <c r="N30" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DarkMeister</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2312</v>
+        <v>0.3428</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0455</v>
+        <v>0.0674</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.519</v>
+        <v>-0.4607</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2312</v>
+        <v>0.3428</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2312</v>
+        <v>0.4371</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1817</v>
+        <v>0.3436</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1817</v>
+        <v>0.3436</v>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.209</v>
+        <v>0.2657</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0411</v>
+        <v>0.0523</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5291</v>
+        <v>-0.4951</v>
       </c>
       <c r="E32" t="n">
-        <v>0.209</v>
+        <v>0.2657</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1024</v>
+        <v>0.1195</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0201</v>
+        <v>0.0235</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5776</v>
+        <v>-0.5604</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1024</v>
+        <v>0.1195</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0318</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0063</v>
+        <v>0.0168</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6097</v>
+        <v>-0.5756</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0318</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0197</v>
+        <v>-0.3327</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0039</v>
+        <v>-0.0654</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6332</v>
+        <v>-0.7624</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0197</v>
+        <v>-0.3327</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0197</v>
+        <v>-0.2791</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0155</v>
+        <v>-0.2194</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0155</v>
+        <v>-0.2194</v>
       </c>
       <c r="N35" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.229</v>
+        <v>-0.3536</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.045</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7284</v>
+        <v>-0.7718</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.229</v>
+        <v>-0.3536</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2791</v>
+        <v>-0.3625</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0549</v>
+        <v>-0.0713</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7513</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2791</v>
+        <v>-0.3625</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2791</v>
+        <v>-0.0197</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2194</v>
+        <v>-0.0155</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.2194</v>
+        <v>-0.0155</v>
       </c>
       <c r="N37" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6612</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1345</v>
+        <v>-0.13</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9356</v>
+        <v>-0.9092</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6612</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7307</v>
+        <v>-0.8917</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1437</v>
+        <v>-0.1754</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9568</v>
+        <v>-1.0121</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7307</v>
+        <v>-0.8917</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-1.4141</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1656</v>
+        <v>-0.2781</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0076</v>
+        <v>-1.2455</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-1.4141</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2036</v>
+        <v>-1.8075</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2367</v>
+        <v>-0.3555</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1721</v>
+        <v>-1.4212</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2036</v>
+        <v>-1.8075</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>

--- a/database/event/8247/event_8247_evp_summary.xlsx
+++ b/database/event/8247/event_8247_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7415</v>
+        <v>7.7468</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5224</v>
+        <v>1.5234</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8441</v>
+        <v>2.9232</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7415</v>
+        <v>7.7468</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.637</v>
+        <v>7.6423</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0032</v>
+        <v>6.0421</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0032</v>
+        <v>6.0421</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7355</v>
+        <v>5.6183</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1279</v>
+        <v>1.1049</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9481</v>
+        <v>1.9536</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7355</v>
+        <v>5.6183</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5078</v>
+        <v>5.3906</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3295</v>
+        <v>4.2619</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3295</v>
+        <v>4.2619</v>
       </c>
       <c r="N3" t="n">
         <v>225</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7617</v>
+        <v>3.6401</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7398</v>
+        <v>0.7158</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0664</v>
+        <v>1.0525</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7617</v>
+        <v>3.6401</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5807</v>
+        <v>3.4591</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8146</v>
+        <v>2.7348</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>186</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8146</v>
+        <v>2.7348</v>
       </c>
       <c r="N4" t="n">
         <v>186</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4405</v>
+        <v>3.5239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6766</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.923</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4405</v>
+        <v>3.5239</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3338</v>
+        <v>3.4172</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6206</v>
+        <v>2.7017</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>225</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6206</v>
+        <v>2.7017</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4205</v>
+        <v>3.4708</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6727</v>
+        <v>0.6825</v>
       </c>
       <c r="D6" t="n">
-        <v>0.914</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4205</v>
+        <v>3.4708</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.446</v>
+        <v>3.4963</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7088</v>
+        <v>2.7642</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7088</v>
+        <v>2.7642</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.194</v>
+        <v>2.1533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4315</v>
+        <v>0.4235</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3662</v>
+        <v>0.3751</v>
       </c>
       <c r="E7" t="n">
-        <v>2.194</v>
+        <v>2.1533</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1396</v>
+        <v>2.0989</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6819</v>
+        <v>1.6594</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>186</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6819</v>
+        <v>1.6594</v>
       </c>
       <c r="N7" t="n">
         <v>186</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7956</v>
+        <v>1.7444</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3531</v>
+        <v>0.343</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1882</v>
+        <v>0.1889</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7956</v>
+        <v>1.7444</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.824</v>
+        <v>1.7728</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4338</v>
+        <v>1.4016</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>152</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4338</v>
+        <v>1.4016</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5561</v>
+        <v>1.5133</v>
       </c>
       <c r="C9" t="n">
-        <v>0.306</v>
+        <v>0.2976</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0813</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5561</v>
+        <v>1.5133</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4141</v>
+        <v>1.3713</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1116</v>
+        <v>1.0842</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>134</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1116</v>
+        <v>1.0842</v>
       </c>
       <c r="N9" t="n">
         <v>134</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4588</v>
+        <v>1.4351</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2869</v>
+        <v>0.2822</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0378</v>
+        <v>0.048</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4588</v>
+        <v>1.4351</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8212</v>
+        <v>0.7975</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6455</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6455</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>38</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.404</v>
+        <v>1.2743</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761</v>
+        <v>0.2506</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0133</v>
+        <v>-0.0253</v>
       </c>
       <c r="E11" t="n">
-        <v>1.404</v>
+        <v>1.2743</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3771</v>
+        <v>1.2474</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0825</v>
+        <v>0.9862</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>134</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0825</v>
+        <v>0.9862</v>
       </c>
       <c r="N11" t="n">
         <v>134</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3459</v>
+        <v>1.2149</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2647</v>
+        <v>0.2389</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0126</v>
+        <v>-0.0523</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3459</v>
+        <v>1.2149</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1094</v>
+        <v>0.9784</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8721</v>
+        <v>0.7735</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>69</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8721</v>
+        <v>0.7735</v>
       </c>
       <c r="N12" t="n">
         <v>69</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.295</v>
+        <v>1.2071</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2547</v>
+        <v>0.2374</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0354</v>
+        <v>-0.0559</v>
       </c>
       <c r="E13" t="n">
-        <v>1.295</v>
+        <v>1.2071</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2246</v>
+        <v>1.1367</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9626</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>152</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9626</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>152</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2864</v>
+        <v>1.1617</v>
       </c>
       <c r="C14" t="n">
-        <v>0.253</v>
+        <v>0.2285</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0392</v>
+        <v>-0.0766</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2864</v>
+        <v>1.1617</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1835</v>
+        <v>1.0588</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9303</v>
+        <v>0.8371</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>89</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9303</v>
+        <v>0.8371</v>
       </c>
       <c r="N14" t="n">
         <v>89</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.244</v>
+        <v>1.0611</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2446</v>
+        <v>0.2087</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0582</v>
+        <v>-0.1224</v>
       </c>
       <c r="E15" t="n">
-        <v>1.244</v>
+        <v>1.0611</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.422</v>
+        <v>1.2391</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1178</v>
+        <v>0.9797</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>134</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1178</v>
+        <v>0.9797</v>
       </c>
       <c r="N15" t="n">
         <v>134</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.03</v>
+        <v>0.9626</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2026</v>
+        <v>0.1893</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1537</v>
+        <v>-0.1673</v>
       </c>
       <c r="E16" t="n">
-        <v>1.03</v>
+        <v>0.9626</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9423</v>
+        <v>0.8749</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7407</v>
+        <v>0.6917</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>89</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7407</v>
+        <v>0.6917</v>
       </c>
       <c r="N16" t="n">
         <v>89</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9826</v>
+        <v>0.8968</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1932</v>
+        <v>0.1764</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1749</v>
+        <v>-0.1973</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9826</v>
+        <v>0.8968</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0143</v>
+        <v>0.9285</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7973</v>
+        <v>0.7341</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>152</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7973</v>
+        <v>0.7341</v>
       </c>
       <c r="N17" t="n">
         <v>152</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9313</v>
+        <v>0.7241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1831</v>
+        <v>0.1424</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1978</v>
+        <v>-0.2759</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9313</v>
+        <v>0.7241</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9564</v>
+        <v>0.7492</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7518</v>
+        <v>0.5924</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>134</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7518</v>
+        <v>0.5924</v>
       </c>
       <c r="N18" t="n">
         <v>134</v>
@@ -1274,26 +1274,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6953</v>
+        <v>0.6669</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1367</v>
+        <v>0.1311</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3032</v>
+        <v>-0.302</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6953</v>
+        <v>0.6669</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6725</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5286</v>
+        <v>0.5543</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5286</v>
+        <v>0.5543</v>
       </c>
       <c r="N19" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.612</v>
+        <v>0.6503</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1204</v>
+        <v>0.1279</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3405</v>
+        <v>-0.3095</v>
       </c>
       <c r="E20" t="n">
-        <v>0.612</v>
+        <v>0.6503</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.455</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3577</v>
+        <v>0.4961</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3577</v>
+        <v>0.4961</v>
       </c>
       <c r="N20" t="n">
-        <v>134</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5976</v>
+        <v>0.6293</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1175</v>
+        <v>0.1238</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3469</v>
+        <v>-0.3191</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5976</v>
+        <v>0.6293</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.639</v>
+        <v>0.4723</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5023</v>
+        <v>0.3734</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5023</v>
+        <v>0.3734</v>
       </c>
       <c r="N21" t="n">
-        <v>186</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5084</v>
+        <v>0.5424</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1</v>
+        <v>0.1067</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3867</v>
+        <v>-0.3587</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5084</v>
+        <v>0.5424</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5426</v>
+        <v>0.7251</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4265</v>
+        <v>0.5733</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>186</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4265</v>
+        <v>0.5733</v>
       </c>
       <c r="N22" t="n">
         <v>186</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5223</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3898</v>
+        <v>-0.3679</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5223</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6842</v>
+        <v>0.5637</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4457</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>186</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4457</v>
       </c>
       <c r="N23" t="n">
         <v>186</v>
@@ -1504,26 +1504,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4898</v>
+        <v>0.4103</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0963</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.395</v>
+        <v>-0.4189</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4898</v>
+        <v>0.4103</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5094</v>
+        <v>0.3381</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4004</v>
+        <v>0.2673</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4004</v>
+        <v>0.2673</v>
       </c>
       <c r="N24" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4733</v>
+        <v>0.3753</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0931</v>
+        <v>0.0738</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4024</v>
+        <v>-0.4348</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4733</v>
+        <v>0.3753</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5109</v>
+        <v>0.3949</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4016</v>
+        <v>0.3122</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4016</v>
+        <v>0.3122</v>
       </c>
       <c r="N25" t="n">
-        <v>225</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4196</v>
+        <v>0.3641</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0825</v>
+        <v>0.0716</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4264</v>
+        <v>-0.4399</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4196</v>
+        <v>0.3641</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3474</v>
+        <v>0.4017</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2731</v>
+        <v>0.3176</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2731</v>
+        <v>0.3176</v>
       </c>
       <c r="N26" t="n">
-        <v>79</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27">
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3958</v>
+        <v>0.3358</v>
       </c>
       <c r="C27" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.437</v>
+        <v>-0.4528</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3958</v>
+        <v>0.3358</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2837</v>
+        <v>0.2237</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.223</v>
+        <v>0.1769</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>0.223</v>
+        <v>0.1769</v>
       </c>
       <c r="N27" t="n">
         <v>38</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tikuak</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3896</v>
+        <v>0.3232</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0766</v>
+        <v>0.0636</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4398</v>
+        <v>-0.4586</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3896</v>
+        <v>0.3232</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4048</v>
+        <v>0.4175</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3182</v>
+        <v>0.3301</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3182</v>
+        <v>0.3301</v>
       </c>
       <c r="N28" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DarkMeister</t>
+          <t>tikuak</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3555</v>
+        <v>0.3074</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0699</v>
+        <v>0.0605</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.455</v>
+        <v>-0.4658</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3555</v>
+        <v>0.3074</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2312</v>
+        <v>0.3226</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1817</v>
+        <v>0.255</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1817</v>
+        <v>0.255</v>
       </c>
       <c r="N29" t="n">
         <v>69</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3544</v>
+        <v>0.2794</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0697</v>
+        <v>0.0549</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4555</v>
+        <v>-0.4785</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3544</v>
+        <v>0.2794</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4002</v>
+        <v>0.3252</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3146</v>
+        <v>0.2571</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>79</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3146</v>
+        <v>0.2571</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1826,26 +1826,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>DarkMeister</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3428</v>
+        <v>0.278</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0674</v>
+        <v>0.0547</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4607</v>
+        <v>-0.4791</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3428</v>
+        <v>0.278</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4371</v>
+        <v>0.1537</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3436</v>
+        <v>0.1216</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3436</v>
+        <v>0.1216</v>
       </c>
       <c r="N31" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2657</v>
+        <v>0.1751</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0523</v>
+        <v>0.0344</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4951</v>
+        <v>-0.526</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2657</v>
+        <v>0.1751</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.209</v>
+        <v>0.1184</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1643</v>
+        <v>0.0936</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>89</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1643</v>
+        <v>0.0936</v>
       </c>
       <c r="N32" t="n">
         <v>89</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1195</v>
+        <v>0.1221</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0235</v>
+        <v>0.024</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5604</v>
+        <v>-0.5502</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1195</v>
+        <v>0.1221</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1024</v>
+        <v>0.105</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0805</v>
+        <v>0.083</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>79</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0805</v>
+        <v>0.083</v>
       </c>
       <c r="N33" t="n">
         <v>79</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0168</v>
+        <v>0.0129</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5756</v>
+        <v>-0.5758</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0318</v>
+        <v>0.0121</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.025</v>
+        <v>0.0095</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>0.025</v>
+        <v>0.0095</v>
       </c>
       <c r="N34" t="n">
         <v>69</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3327</v>
+        <v>-0.3383</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0654</v>
+        <v>-0.0665</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7624</v>
+        <v>-0.7599</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3327</v>
+        <v>-0.3383</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2791</v>
+        <v>-0.2847</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2194</v>
+        <v>-0.2251</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>79</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2194</v>
+        <v>-0.2251</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
@@ -2056,26 +2056,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3536</v>
+        <v>-0.412</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7718</v>
+        <v>-0.7935</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3536</v>
+        <v>-0.412</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.229</v>
+        <v>-0.0692</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,44 +2084,44 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.18</v>
+        <v>-0.0547</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.18</v>
+        <v>-0.0547</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3625</v>
+        <v>-0.4258</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0713</v>
+        <v>-0.0837</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.7998</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3625</v>
+        <v>-0.4258</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0197</v>
+        <v>-0.3012</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0155</v>
+        <v>-0.2381</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0155</v>
+        <v>-0.2381</v>
       </c>
       <c r="N37" t="n">
-        <v>38</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38">
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6612</v>
+        <v>-0.6067</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.13</v>
+        <v>-0.1193</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9092</v>
+        <v>-0.8822</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6612</v>
+        <v>-0.6067</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5377</v>
+        <v>-0.4977</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>89</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.5377</v>
+        <v>-0.4977</v>
       </c>
       <c r="N38" t="n">
         <v>89</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8917</v>
+        <v>-0.8174</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1754</v>
+        <v>-0.1607</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0121</v>
+        <v>-0.9782</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8917</v>
+        <v>-0.8174</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7307</v>
+        <v>-0.6564</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5744</v>
+        <v>-0.519</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>69</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.5744</v>
+        <v>-0.519</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4141</v>
+        <v>-1.3733</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2781</v>
+        <v>-0.2701</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2455</v>
+        <v>-1.2314</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4141</v>
+        <v>-1.3733</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8014</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.662</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.662</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>38</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8075</v>
+        <v>-1.792</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3555</v>
+        <v>-0.3524</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4212</v>
+        <v>-1.4221</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8075</v>
+        <v>-1.792</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2036</v>
+        <v>-1.1881</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9393</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9393</v>
       </c>
       <c r="N41" t="n">
         <v>38</v>
@@ -2429,10 +2429,10 @@
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2686</v>
+        <v>0.2228</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6406</v>
+        <v>4.6788</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1241</v>
+        <v>-0.1086</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.6061</v>
+        <v>-2.2806</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1989</v>
+        <v>-0.1804</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.1769</v>
+        <v>-3.7884</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.277</v>
+        <v>-0.2585</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.817</v>
+        <v>-5.4285</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3698</v>
+        <v>-0.3559</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.7658</v>
+        <v>-7.4739</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7577</v>
+        <v>1.7989</v>
       </c>
       <c r="J7" t="n">
-        <v>36.9117</v>
+        <v>37.7769</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9735</v>
+        <v>0.9646</v>
       </c>
       <c r="J8" t="n">
-        <v>20.4435</v>
+        <v>20.2566</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3998</v>
+        <v>0.3672</v>
       </c>
       <c r="J9" t="n">
-        <v>8.395799999999999</v>
+        <v>7.7112</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0149</v>
+        <v>0.0048</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3129</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5182</v>
+        <v>-0.4811</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.8822</v>
+        <v>-10.1031</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1203</v>
+        <v>-0.1038</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0451</v>
+        <v>-1.7646</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1203</v>
+        <v>-0.1038</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0451</v>
+        <v>-1.7646</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.422</v>
+        <v>-0.4127</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.174</v>
+        <v>-7.0159</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4485</v>
+        <v>-0.4414</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.6245</v>
+        <v>-7.5038</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4661</v>
+        <v>-0.4607</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.9237</v>
+        <v>-7.8319</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6613</v>
+        <v>1.6907</v>
       </c>
       <c r="J17" t="n">
-        <v>28.2421</v>
+        <v>28.7419</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1.558</v>
+        <v>1.5868</v>
       </c>
       <c r="J18" t="n">
-        <v>26.486</v>
+        <v>26.9756</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7657</v>
+        <v>0.7492</v>
       </c>
       <c r="J19" t="n">
-        <v>13.0169</v>
+        <v>12.7364</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3777</v>
+        <v>0.3457</v>
       </c>
       <c r="J20" t="n">
-        <v>6.4209</v>
+        <v>5.8769</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.301</v>
+        <v>-0.2679</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.117</v>
+        <v>-4.5543</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4993</v>
+        <v>0.4309</v>
       </c>
       <c r="J22" t="n">
-        <v>10.9846</v>
+        <v>9.479799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4216</v>
+        <v>0.3571</v>
       </c>
       <c r="J23" t="n">
-        <v>9.2752</v>
+        <v>7.8562</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="J24" t="n">
-        <v>2.189</v>
+        <v>1.6324</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0212</v>
+        <v>0.0136</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4664</v>
+        <v>0.2992</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.92</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1344</v>
+        <v>-0.1152</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.9568</v>
+        <v>-2.5344</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2999</v>
+        <v>0.2885</v>
       </c>
       <c r="J27" t="n">
-        <v>6.5978</v>
+        <v>6.347</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.108</v>
+        <v>0.0919</v>
       </c>
       <c r="J28" t="n">
-        <v>2.376</v>
+        <v>2.0218</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.849</v>
+        <v>-2.4618</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.6122</v>
+        <v>-5.1788</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.322</v>
+        <v>-0.3051</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.084</v>
+        <v>-6.7122</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6587</v>
+        <v>0.6009</v>
       </c>
       <c r="J32" t="n">
-        <v>15.1501</v>
+        <v>13.8207</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0023</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.124</v>
+        <v>-0.1054</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.852</v>
+        <v>-2.4242</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1473</v>
+        <v>-0.1276</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.3879</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1913</v>
+        <v>-0.1706</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.3999</v>
+        <v>-3.9238</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9909</v>
+        <v>0.9818</v>
       </c>
       <c r="J37" t="n">
-        <v>22.7907</v>
+        <v>22.5814</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7905</v>
+        <v>0.7635</v>
       </c>
       <c r="J38" t="n">
-        <v>18.1815</v>
+        <v>17.5605</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.98</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1212</v>
+        <v>-0.0941</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.7876</v>
+        <v>-2.1643</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.98</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1212</v>
+        <v>-0.0941</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.7876</v>
+        <v>-2.1643</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2539</v>
+        <v>-0.215</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.8397</v>
+        <v>-4.945</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5442</v>
+        <v>0.5074</v>
       </c>
       <c r="J42" t="n">
-        <v>10.3398</v>
+        <v>9.640599999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.498</v>
+        <v>0.4504</v>
       </c>
       <c r="J43" t="n">
-        <v>9.462</v>
+        <v>8.557600000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.26</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3667</v>
+        <v>0.308</v>
       </c>
       <c r="J44" t="n">
-        <v>6.9673</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2492</v>
+        <v>0.2029</v>
       </c>
       <c r="J45" t="n">
-        <v>4.7348</v>
+        <v>3.8551</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2601</v>
+        <v>-0.2422</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.9419</v>
+        <v>-4.6018</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.341</v>
+        <v>0.3332</v>
       </c>
       <c r="J47" t="n">
-        <v>6.479</v>
+        <v>6.3308</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0421</v>
+        <v>0.032</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1066</v>
+        <v>-0.0906</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.0254</v>
+        <v>-1.7214</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.77</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.275</v>
+        <v>-0.2559</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.225</v>
+        <v>-4.8621</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3036</v>
+        <v>-0.2857</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.7684</v>
+        <v>-5.4283</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5084</v>
+        <v>0.4749</v>
       </c>
       <c r="J52" t="n">
-        <v>11.1848</v>
+        <v>10.4478</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4127</v>
+        <v>0.357</v>
       </c>
       <c r="J53" t="n">
-        <v>9.0794</v>
+        <v>7.854</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1309</v>
+        <v>-0.1128</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.8798</v>
+        <v>-2.4816</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3146</v>
+        <v>-0.2973</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.9212</v>
+        <v>-6.5406</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.388</v>
+        <v>-0.3761</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.536</v>
+        <v>-8.2742</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.3</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6825</v>
+        <v>0.6677</v>
       </c>
       <c r="J57" t="n">
-        <v>15.015</v>
+        <v>14.6894</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6049</v>
+        <v>0.5928</v>
       </c>
       <c r="J58" t="n">
-        <v>13.3078</v>
+        <v>13.0416</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3709</v>
+        <v>0.3339</v>
       </c>
       <c r="J59" t="n">
-        <v>8.159800000000001</v>
+        <v>7.3458</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1499</v>
+        <v>0.125</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2978</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2551</v>
+        <v>-0.2162</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.6122</v>
+        <v>-4.7564</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.19</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4502</v>
+        <v>0.402</v>
       </c>
       <c r="J62" t="n">
-        <v>9.904400000000001</v>
+        <v>8.843999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1518</v>
+        <v>0.1176</v>
       </c>
       <c r="J63" t="n">
-        <v>3.3396</v>
+        <v>2.5872</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.78</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.7024</v>
+        <v>-5.2822</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3713</v>
+        <v>-0.3576</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.1686</v>
+        <v>-7.8672</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3713</v>
+        <v>-0.3576</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.1686</v>
+        <v>-7.8672</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1816</v>
+        <v>1.1781</v>
       </c>
       <c r="J67" t="n">
-        <v>25.9952</v>
+        <v>25.9182</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.33</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7138</v>
+        <v>0.6998</v>
       </c>
       <c r="J68" t="n">
-        <v>15.7036</v>
+        <v>15.3956</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.31</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6843</v>
+        <v>0.6712</v>
       </c>
       <c r="J69" t="n">
-        <v>15.0546</v>
+        <v>14.7664</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2818</v>
+        <v>0.2501</v>
       </c>
       <c r="J70" t="n">
-        <v>6.1996</v>
+        <v>5.5022</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9302</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.4644</v>
+        <v>-20.3258</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2102</v>
+        <v>0.1706</v>
       </c>
       <c r="J72" t="n">
-        <v>3.9938</v>
+        <v>3.2414</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1623</v>
+        <v>0.1283</v>
       </c>
       <c r="J73" t="n">
-        <v>3.0837</v>
+        <v>2.4377</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0321</v>
+        <v>0.0263</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6099</v>
+        <v>0.4997</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.54</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.474</v>
+        <v>-0.4701</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.006</v>
+        <v>-8.931900000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5</v>
+        <v>-0.4994</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.5</v>
+        <v>-9.4886</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0333</v>
+        <v>1.022</v>
       </c>
       <c r="J77" t="n">
-        <v>19.6327</v>
+        <v>19.418</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.53</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9675</v>
       </c>
       <c r="J78" t="n">
-        <v>18.6257</v>
+        <v>18.3825</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5414</v>
+        <v>0.5373</v>
       </c>
       <c r="J79" t="n">
-        <v>10.2866</v>
+        <v>10.2087</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2693</v>
+        <v>0.2384</v>
       </c>
       <c r="J80" t="n">
-        <v>5.1167</v>
+        <v>4.5296</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0892</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>1.6948</v>
+        <v>1.3015</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.451</v>
+        <v>0.3902</v>
       </c>
       <c r="J82" t="n">
-        <v>9.922000000000001</v>
+        <v>8.5844</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3535</v>
+        <v>0.2939</v>
       </c>
       <c r="J83" t="n">
-        <v>7.777</v>
+        <v>6.4658</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2932</v>
+        <v>0.2394</v>
       </c>
       <c r="J84" t="n">
-        <v>6.4504</v>
+        <v>5.2668</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.05</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1004</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>2.2088</v>
+        <v>1.6478</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2725</v>
+        <v>-0.2541</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.995</v>
+        <v>-5.5902</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.192</v>
+        <v>0.175</v>
       </c>
       <c r="J87" t="n">
-        <v>4.224</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1421</v>
+        <v>0.1249</v>
       </c>
       <c r="J88" t="n">
-        <v>3.1262</v>
+        <v>2.7478</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1421</v>
+        <v>0.1249</v>
       </c>
       <c r="J89" t="n">
-        <v>3.1262</v>
+        <v>2.7478</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2367</v>
+        <v>-0.2166</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.2074</v>
+        <v>-4.7652</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3694</v>
+        <v>-0.3559</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.126799999999999</v>
+        <v>-7.8298</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4676</v>
+        <v>0.4192</v>
       </c>
       <c r="J92" t="n">
-        <v>11.2224</v>
+        <v>10.0608</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.323</v>
+        <v>0.2711</v>
       </c>
       <c r="J93" t="n">
-        <v>7.752</v>
+        <v>6.5064</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.04</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1215</v>
+        <v>0.0924</v>
       </c>
       <c r="J94" t="n">
-        <v>2.916</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1716</v>
+        <v>-0.1511</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.1184</v>
+        <v>-3.6264</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2142</v>
+        <v>-0.1936</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.1408</v>
+        <v>-4.6464</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9524</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>22.8576</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5463</v>
+        <v>0.5346</v>
       </c>
       <c r="J98" t="n">
-        <v>13.1112</v>
+        <v>12.8304</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4214</v>
+        <v>-0.3784</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.1136</v>
+        <v>-9.0816</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6353</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-15.2472</v>
+        <v>-14.3592</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7245</v>
+        <v>-0.6932</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.388</v>
+        <v>-16.6368</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6468</v>
+        <v>0.6073</v>
       </c>
       <c r="J102" t="n">
-        <v>14.8764</v>
+        <v>13.9679</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.24</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3585</v>
+        <v>0.2981</v>
       </c>
       <c r="J103" t="n">
-        <v>8.2455</v>
+        <v>6.8563</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0866</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>1.9918</v>
+        <v>1.4536</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2496</v>
+        <v>-0.23</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.7408</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.308</v>
+        <v>-0.2912</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.084</v>
+        <v>-6.6976</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5334</v>
+        <v>0.5647</v>
       </c>
       <c r="J107" t="n">
-        <v>12.2682</v>
+        <v>12.9881</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0092</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.9665</v>
+        <v>-1.6077</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2317</v>
+        <v>-0.2113</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.3291</v>
+        <v>-4.8599</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2417</v>
+        <v>-0.2215</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.5591</v>
+        <v>-5.0945</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7275</v>
+        <v>0.6922</v>
       </c>
       <c r="J112" t="n">
-        <v>26.19</v>
+        <v>24.9192</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2026</v>
+        <v>0.1637</v>
       </c>
       <c r="J113" t="n">
-        <v>7.2936</v>
+        <v>5.8932</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0052</v>
+        <v>-0.0035</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.1872</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0052</v>
+        <v>-0.0035</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.1872</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.85</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2085</v>
+        <v>-0.188</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.506</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.61</v>
       </c>
       <c r="I117" t="n">
-        <v>1.123</v>
+        <v>1.1179</v>
       </c>
       <c r="J117" t="n">
-        <v>40.428</v>
+        <v>40.2444</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.15</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4377</v>
+        <v>0.4029</v>
       </c>
       <c r="J118" t="n">
-        <v>15.7572</v>
+        <v>14.5044</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3943</v>
+        <v>0.3571</v>
       </c>
       <c r="J119" t="n">
-        <v>14.1948</v>
+        <v>12.8556</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2855</v>
+        <v>-0.2453</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.278</v>
+        <v>-8.8308</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.86</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4712</v>
+        <v>-0.4296</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.9632</v>
+        <v>-15.4656</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.12</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2887</v>
+        <v>0.2391</v>
       </c>
       <c r="J122" t="n">
-        <v>8.661</v>
+        <v>7.173</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2697</v>
+        <v>0.2218</v>
       </c>
       <c r="J123" t="n">
-        <v>8.090999999999999</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2504</v>
+        <v>0.2043</v>
       </c>
       <c r="J124" t="n">
-        <v>7.512</v>
+        <v>6.129</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0589</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.202</v>
+        <v>-1.767</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2829</v>
+        <v>-0.2642</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.487</v>
+        <v>-7.926</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6449</v>
+        <v>0.6306</v>
       </c>
       <c r="J127" t="n">
-        <v>19.347</v>
+        <v>18.918</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4446</v>
+        <v>0.4084</v>
       </c>
       <c r="J128" t="n">
-        <v>13.338</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1888</v>
+        <v>0.1592</v>
       </c>
       <c r="J129" t="n">
-        <v>5.664</v>
+        <v>4.776</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1241</v>
+        <v>0.1011</v>
       </c>
       <c r="J130" t="n">
-        <v>3.723</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3041</v>
+        <v>-0.2627</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.122999999999999</v>
+        <v>-7.881</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8656</v>
+        <v>0.85</v>
       </c>
       <c r="J132" t="n">
-        <v>24.2368</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6604</v>
+        <v>0.647</v>
       </c>
       <c r="J133" t="n">
-        <v>18.4912</v>
+        <v>18.116</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.2</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5198</v>
+        <v>0.5091</v>
       </c>
       <c r="J134" t="n">
-        <v>14.5544</v>
+        <v>14.2548</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1094</v>
+        <v>0.0886</v>
       </c>
       <c r="J135" t="n">
-        <v>3.0632</v>
+        <v>2.4808</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3748</v>
+        <v>-0.3331</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.4944</v>
+        <v>-9.3268</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1634</v>
+        <v>0.1265</v>
       </c>
       <c r="J137" t="n">
-        <v>4.5752</v>
+        <v>3.542</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1396</v>
+        <v>0.106</v>
       </c>
       <c r="J138" t="n">
-        <v>3.9088</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0561</v>
+        <v>0.0382</v>
       </c>
       <c r="J139" t="n">
-        <v>1.5708</v>
+        <v>1.0696</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.3948</v>
+        <v>-6.8516</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3398</v>
+        <v>-0.324</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.5144</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.28</v>
       </c>
       <c r="I142" t="n">
-        <v>0.461</v>
+        <v>0.4787</v>
       </c>
       <c r="J142" t="n">
-        <v>9.220000000000001</v>
+        <v>9.574</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2126</v>
+        <v>-0.1929</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.252</v>
+        <v>-3.858</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2227</v>
+        <v>-0.2029</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.454</v>
+        <v>-4.058</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2524</v>
+        <v>-0.2329</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.048</v>
+        <v>-4.658</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2814</v>
+        <v>-0.2627</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.628</v>
+        <v>-5.254</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.68</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6986</v>
+        <v>0.6532</v>
       </c>
       <c r="J147" t="n">
-        <v>13.972</v>
+        <v>13.064</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.46</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5017</v>
       </c>
       <c r="J148" t="n">
-        <v>10.776</v>
+        <v>10.034</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.4</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4932</v>
+        <v>0.4451</v>
       </c>
       <c r="J149" t="n">
-        <v>9.864000000000001</v>
+        <v>8.901999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1074</v>
+        <v>-0.0911</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.148</v>
+        <v>-1.822</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1911</v>
+        <v>-0.1722</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.822</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1194</v>
+        <v>1.1123</v>
       </c>
       <c r="J152" t="n">
-        <v>23.5074</v>
+        <v>23.3583</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.14</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4098</v>
+        <v>0.3757</v>
       </c>
       <c r="J153" t="n">
-        <v>8.6058</v>
+        <v>7.8897</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3106</v>
+        <v>0.2777</v>
       </c>
       <c r="J154" t="n">
-        <v>6.5226</v>
+        <v>5.8317</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.08</v>
       </c>
       <c r="I155" t="n">
-        <v>0.257</v>
+        <v>0.226</v>
       </c>
       <c r="J155" t="n">
-        <v>5.397</v>
+        <v>4.746</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1698</v>
+        <v>0.1436</v>
       </c>
       <c r="J156" t="n">
-        <v>3.5658</v>
+        <v>3.0156</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.08</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2332</v>
+        <v>0.1886</v>
       </c>
       <c r="J157" t="n">
-        <v>4.8972</v>
+        <v>3.9606</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1174</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>2.4654</v>
+        <v>1.8375</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1284</v>
+        <v>-0.1115</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.6964</v>
+        <v>-2.3415</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2029</v>
+        <v>-0.1832</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.2609</v>
+        <v>-3.8472</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.384</v>
+        <v>-0.3714</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.064</v>
+        <v>-7.7994</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.39</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5036</v>
+        <v>0.4573</v>
       </c>
       <c r="J162" t="n">
-        <v>11.5828</v>
+        <v>10.5179</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2186</v>
+        <v>0.1733</v>
       </c>
       <c r="J163" t="n">
-        <v>5.0278</v>
+        <v>3.9859</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.04</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0852</v>
+        <v>0.0623</v>
       </c>
       <c r="J164" t="n">
-        <v>1.9596</v>
+        <v>1.4329</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.99</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0322</v>
+        <v>-0.0233</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.7406</v>
+        <v>-0.5359</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.107</v>
+        <v>-0.0892</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.461</v>
+        <v>-2.0516</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3931</v>
+        <v>0.3908</v>
       </c>
       <c r="J167" t="n">
-        <v>9.0413</v>
+        <v>8.9884</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3529</v>
+        <v>0.3461</v>
       </c>
       <c r="J168" t="n">
-        <v>8.1167</v>
+        <v>7.9603</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.5144</v>
+        <v>-3.0774</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.5144</v>
+        <v>-3.0774</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.47</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5434</v>
+        <v>-0.5505</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.4982</v>
+        <v>-12.6615</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.37</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6212</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>24.848</v>
+        <v>23.648</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.33</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5766</v>
+        <v>0.5496</v>
       </c>
       <c r="J173" t="n">
-        <v>23.064</v>
+        <v>21.984</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1176</v>
+        <v>0.0906</v>
       </c>
       <c r="J174" t="n">
-        <v>4.704</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.84</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2182</v>
+        <v>-0.1978</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.728</v>
+        <v>-7.912</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.78</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2784</v>
+        <v>-0.2598</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.136</v>
+        <v>-10.392</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0903</v>
+        <v>1.0826</v>
       </c>
       <c r="J177" t="n">
-        <v>43.612</v>
+        <v>43.304</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4886</v>
+        <v>0.4693</v>
       </c>
       <c r="J178" t="n">
-        <v>19.544</v>
+        <v>18.772</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3677</v>
+        <v>0.332</v>
       </c>
       <c r="J179" t="n">
-        <v>14.708</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3172</v>
+        <v>0.2829</v>
       </c>
       <c r="J180" t="n">
-        <v>12.688</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6407</v>
+        <v>-0.6066</v>
       </c>
       <c r="J181" t="n">
-        <v>-25.628</v>
+        <v>-24.264</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.41</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7218</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>11.5488</v>
+        <v>11.1536</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2198</v>
+        <v>-0.2006</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.5168</v>
+        <v>-3.2096</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3066</v>
+        <v>-0.289</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.9056</v>
+        <v>-4.624</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3159</v>
+        <v>-0.2987</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.0544</v>
+        <v>-4.7792</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3891</v>
+        <v>-0.3768</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.2256</v>
+        <v>-6.0288</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.09</v>
       </c>
       <c r="I187" t="n">
-        <v>1.649</v>
+        <v>1.6831</v>
       </c>
       <c r="J187" t="n">
-        <v>26.384</v>
+        <v>26.9296</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.32</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6815</v>
+        <v>0.6746</v>
       </c>
       <c r="J188" t="n">
-        <v>10.904</v>
+        <v>10.7936</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6669</v>
+        <v>0.6606</v>
       </c>
       <c r="J189" t="n">
-        <v>10.6704</v>
+        <v>10.5696</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4972</v>
+        <v>0.4882</v>
       </c>
       <c r="J190" t="n">
-        <v>7.9552</v>
+        <v>7.8112</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1966</v>
+        <v>0.1664</v>
       </c>
       <c r="J191" t="n">
-        <v>3.1456</v>
+        <v>2.6624</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9267</v>
+        <v>0.8986</v>
       </c>
       <c r="J192" t="n">
-        <v>18.534</v>
+        <v>17.972</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.06</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1818</v>
+        <v>0.1425</v>
       </c>
       <c r="J193" t="n">
-        <v>3.636</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2264</v>
+        <v>-0.2062</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.528</v>
+        <v>-4.124</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4229</v>
+        <v>-0.4144</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.458</v>
+        <v>-8.288</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4579</v>
+        <v>-0.4534</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.157999999999999</v>
+        <v>-9.068</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.407</v>
+        <v>1.4198</v>
       </c>
       <c r="J197" t="n">
-        <v>28.14</v>
+        <v>28.396</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7773</v>
+        <v>0.7635</v>
       </c>
       <c r="J198" t="n">
-        <v>15.546</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.511</v>
+        <v>0.5031</v>
       </c>
       <c r="J199" t="n">
-        <v>10.22</v>
+        <v>10.062</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.01</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0139</v>
+        <v>0.0037</v>
       </c>
       <c r="J200" t="n">
-        <v>0.278</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3654</v>
+        <v>-0.3263</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.308</v>
+        <v>-6.526</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4074</v>
+        <v>0.3597</v>
       </c>
       <c r="J202" t="n">
-        <v>7.3332</v>
+        <v>6.4746</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0412</v>
+        <v>0.0356</v>
       </c>
       <c r="J203" t="n">
-        <v>0.7416</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2812</v>
+        <v>-0.2637</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.0616</v>
+        <v>-4.7466</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.58</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4356</v>
+        <v>-0.4274</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.8408</v>
+        <v>-7.6932</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.52</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4882</v>
+        <v>-0.4859</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.787599999999999</v>
+        <v>-8.7462</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.2</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8005</v>
+        <v>1.8581</v>
       </c>
       <c r="J207" t="n">
-        <v>32.409</v>
+        <v>33.4458</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.41</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8129</v>
+        <v>0.8001</v>
       </c>
       <c r="J208" t="n">
-        <v>14.6322</v>
+        <v>14.4018</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.09</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2642</v>
+        <v>0.2332</v>
       </c>
       <c r="J209" t="n">
-        <v>4.7556</v>
+        <v>4.1976</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1136</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.0448</v>
+        <v>-1.6956</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.373</v>
+        <v>-0.3353</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.714</v>
+        <v>-6.0354</v>
       </c>
     </row>
   </sheetData>
